--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -911,6 +911,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1031,7 +1035,7 @@
         <v>41500</v>
       </c>
       <c r="E4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F4">
         <v>70000</v>
@@ -1101,7 +1105,7 @@
         <v>41500</v>
       </c>
       <c r="E6">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F6">
         <v>70000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6948"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Q2_plan</t>
+  </si>
+  <si>
+    <t>Q2_achievement</t>
   </si>
   <si>
     <t>fee_charge</t>
@@ -909,14 +912,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -950,13 +955,16 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>37500</v>
@@ -965,17 +973,17 @@
         <v>41500</v>
       </c>
       <c r="E2">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F2">
         <v>70000</v>
       </c>
       <c r="G2">
+        <v>70000</v>
+      </c>
+      <c r="H2">
         <v>242</v>
       </c>
-      <c r="H2">
-        <v>25500</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
@@ -983,15 +991,18 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>59000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>37500</v>
@@ -1000,33 +1011,36 @@
         <v>41500</v>
       </c>
       <c r="E3">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F3">
         <v>70000</v>
       </c>
       <c r="G3">
-        <v>650</v>
+        <v>82000</v>
       </c>
       <c r="H3">
-        <v>20000</v>
+        <v>2400</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>13000</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>37500</v>
@@ -1041,27 +1055,30 @@
         <v>70000</v>
       </c>
       <c r="G4">
+        <v>46500</v>
+      </c>
+      <c r="H4">
         <v>650</v>
       </c>
-      <c r="H4">
-        <v>2000</v>
-      </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>13000</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>46500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>37500</v>
@@ -1076,7 +1093,7 @@
         <v>70000</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1085,18 +1102,21 @@
         <v>0</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>6900</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>43500</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>37500</v>
@@ -1111,27 +1131,30 @@
         <v>70000</v>
       </c>
       <c r="G6">
+        <v>45500</v>
+      </c>
+      <c r="H6">
         <v>892</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>13000</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
       <c r="K6">
-        <v>43500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>37500</v>
@@ -1146,27 +1169,30 @@
         <v>70000</v>
       </c>
       <c r="G7">
+        <v>43500</v>
+      </c>
+      <c r="H7">
         <v>650</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>13000</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>37500</v>
@@ -1175,13 +1201,13 @@
         <v>41500</v>
       </c>
       <c r="E8">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F8">
         <v>70000</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>44500</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1193,15 +1219,18 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>37500</v>
@@ -1216,27 +1245,30 @@
         <v>70000</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>81000</v>
       </c>
       <c r="H9">
-        <v>37500</v>
+        <v>650</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
+        <v>13000</v>
+      </c>
+      <c r="K9">
         <v>200</v>
       </c>
-      <c r="K9">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>81000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>37500</v>
@@ -1251,7 +1283,7 @@
         <v>70000</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1263,15 +1295,18 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>37500</v>
@@ -1280,33 +1315,36 @@
         <v>41500</v>
       </c>
       <c r="E11">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F11">
         <v>70000</v>
       </c>
       <c r="G11">
-        <v>650</v>
+        <v>82000</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>13000</v>
       </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
       <c r="K11">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>37500</v>
@@ -1315,13 +1353,13 @@
         <v>41500</v>
       </c>
       <c r="E12">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F12">
         <v>70000</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>44500</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1333,15 +1371,18 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>37500</v>
@@ -1350,16 +1391,16 @@
         <v>41500</v>
       </c>
       <c r="E13">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F13">
         <v>70000</v>
       </c>
       <c r="G13">
-        <v>200</v>
+        <v>82000</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3950</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1368,15 +1409,18 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14">
         <v>37500</v>
@@ -1391,11 +1435,11 @@
         <v>70000</v>
       </c>
       <c r="G14">
+        <v>81000</v>
+      </c>
+      <c r="H14">
         <v>287</v>
       </c>
-      <c r="H14">
-        <v>37500</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -1403,15 +1447,18 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>81000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15">
         <v>37500</v>
@@ -1420,16 +1467,16 @@
         <v>41500</v>
       </c>
       <c r="E15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F15">
         <v>70000</v>
       </c>
       <c r="G15">
-        <v>500</v>
+        <v>82000</v>
       </c>
       <c r="H15">
-        <v>30000</v>
+        <v>1250</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1438,34 +1485,37 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>37500</v>
       </c>
       <c r="D16">
-        <v>13000</v>
+        <v>27000</v>
       </c>
       <c r="E16">
+        <v>3000</v>
+      </c>
+      <c r="F16">
+        <v>70000</v>
+      </c>
+      <c r="G16">
+        <v>30000</v>
+      </c>
+      <c r="H16">
         <v>2000</v>
       </c>
-      <c r="F16">
-        <v>70000</v>
-      </c>
-      <c r="G16">
-        <v>2000</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -1473,15 +1523,18 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>37500</v>
@@ -1496,11 +1549,11 @@
         <v>70000</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>2000</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -1510,13 +1563,16 @@
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1017</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>37500</v>
@@ -1525,17 +1581,17 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F18">
         <v>70000</v>
       </c>
       <c r="G18">
+        <v>1000</v>
+      </c>
+      <c r="H18">
         <v>2000</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -1544,6 +1600,9 @@
       </c>
       <c r="K18">
         <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -915,6 +915,8 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1277,13 +1279,13 @@
         <v>41500</v>
       </c>
       <c r="E10">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F10">
         <v>70000</v>
       </c>
       <c r="G10">
-        <v>43500</v>
+        <v>44500</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1298,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>43500</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -19,20 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Q1_plan</t>
-  </si>
-  <si>
-    <t>Q1_achievement</t>
-  </si>
-  <si>
     <t>Monthly_payment_Q2</t>
   </si>
   <si>
@@ -45,18 +36,9 @@
     <t>fee_charge</t>
   </si>
   <si>
-    <t>volentary_saving</t>
-  </si>
-  <si>
     <t>Benefit_gain</t>
   </si>
   <si>
-    <t>Expenditure</t>
-  </si>
-  <si>
-    <t>total_payr</t>
-  </si>
-  <si>
     <t>Geetu Bekela</t>
   </si>
   <si>
@@ -106,6 +88,9 @@
   </si>
   <si>
     <t>Naggasaa Dheeressaa</t>
+  </si>
+  <si>
+    <t>Bacha ifa</t>
   </si>
 </sst>
 </file>
@@ -912,18 +897,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -942,669 +919,365 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2">
+        <v>3000</v>
+      </c>
+      <c r="C2">
+        <v>70000</v>
+      </c>
+      <c r="D2">
+        <v>70000</v>
+      </c>
+      <c r="E2">
+        <v>242</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B3">
+        <v>3000</v>
+      </c>
+      <c r="C3">
+        <v>70000</v>
+      </c>
+      <c r="D3">
+        <v>82000</v>
+      </c>
+      <c r="E3">
+        <v>2400</v>
+      </c>
+      <c r="F3">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B4">
+        <v>3000</v>
+      </c>
+      <c r="C4">
+        <v>70000</v>
+      </c>
+      <c r="D4">
+        <v>46500</v>
+      </c>
+      <c r="E4">
+        <v>650</v>
+      </c>
+      <c r="F4">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B5">
+        <v>2000</v>
+      </c>
+      <c r="C5">
+        <v>70000</v>
+      </c>
+      <c r="D5">
+        <v>43500</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B6">
+        <v>4000</v>
+      </c>
+      <c r="C6">
+        <v>70000</v>
+      </c>
+      <c r="D6">
+        <v>45500</v>
+      </c>
+      <c r="E6">
+        <v>892</v>
+      </c>
+      <c r="F6">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B7">
+        <v>2000</v>
+      </c>
+      <c r="C7">
+        <v>70000</v>
+      </c>
+      <c r="D7">
+        <v>43500</v>
+      </c>
+      <c r="E7">
+        <v>650</v>
+      </c>
+      <c r="F7">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="C2">
-        <v>37500</v>
-      </c>
-      <c r="D2">
-        <v>41500</v>
-      </c>
-      <c r="E2">
+      <c r="B8">
         <v>3000</v>
       </c>
-      <c r="F2">
-        <v>70000</v>
-      </c>
-      <c r="G2">
-        <v>70000</v>
-      </c>
-      <c r="H2">
-        <v>242</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C8">
+        <v>70000</v>
+      </c>
+      <c r="D8">
+        <v>44500</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>37500</v>
-      </c>
-      <c r="D3">
-        <v>41500</v>
-      </c>
-      <c r="E3">
+      <c r="B9">
+        <v>2000</v>
+      </c>
+      <c r="C9">
+        <v>70000</v>
+      </c>
+      <c r="D9">
+        <v>81000</v>
+      </c>
+      <c r="E9">
+        <v>650</v>
+      </c>
+      <c r="F9">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
         <v>3000</v>
       </c>
-      <c r="F3">
-        <v>70000</v>
-      </c>
-      <c r="G3">
+      <c r="C10">
+        <v>70000</v>
+      </c>
+      <c r="D10">
+        <v>44500</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>3000</v>
+      </c>
+      <c r="C11">
+        <v>70000</v>
+      </c>
+      <c r="D11">
         <v>82000</v>
       </c>
-      <c r="H3">
-        <v>2400</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="E11">
+        <v>4400</v>
+      </c>
+      <c r="F11">
         <v>13000</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>3000</v>
+      </c>
+      <c r="C12">
+        <v>70000</v>
+      </c>
+      <c r="D12">
+        <v>44500</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>3000</v>
+      </c>
+      <c r="C13">
+        <v>70000</v>
+      </c>
+      <c r="D13">
         <v>82000</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>37500</v>
-      </c>
-      <c r="D4">
-        <v>41500</v>
-      </c>
-      <c r="E4">
+      <c r="E13">
+        <v>3950</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>2000</v>
+      </c>
+      <c r="C14">
+        <v>70000</v>
+      </c>
+      <c r="D14">
+        <v>81000</v>
+      </c>
+      <c r="E14">
+        <v>287</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
         <v>3000</v>
       </c>
-      <c r="F4">
-        <v>70000</v>
-      </c>
-      <c r="G4">
-        <v>46500</v>
-      </c>
-      <c r="H4">
-        <v>650</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>13000</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>46500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>37500</v>
-      </c>
-      <c r="D5">
-        <v>41500</v>
-      </c>
-      <c r="E5">
+      <c r="C15">
+        <v>70000</v>
+      </c>
+      <c r="D15">
+        <v>82000</v>
+      </c>
+      <c r="E15">
+        <v>1250</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>3000</v>
+      </c>
+      <c r="C16">
+        <v>70000</v>
+      </c>
+      <c r="D16">
+        <v>30000</v>
+      </c>
+      <c r="E16">
         <v>2000</v>
       </c>
-      <c r="F5">
-        <v>70000</v>
-      </c>
-      <c r="G5">
-        <v>43500</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>6900</v>
-      </c>
-      <c r="L5">
-        <v>43500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>37500</v>
-      </c>
-      <c r="D6">
-        <v>41500</v>
-      </c>
-      <c r="E6">
-        <v>4000</v>
-      </c>
-      <c r="F6">
-        <v>70000</v>
-      </c>
-      <c r="G6">
-        <v>45500</v>
-      </c>
-      <c r="H6">
-        <v>892</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>13000</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>37500</v>
-      </c>
-      <c r="D7">
-        <v>41500</v>
-      </c>
-      <c r="E7">
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>70000</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>2000</v>
       </c>
-      <c r="F7">
-        <v>70000</v>
-      </c>
-      <c r="G7">
-        <v>43500</v>
-      </c>
-      <c r="H7">
-        <v>650</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>13000</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>43500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>37500</v>
-      </c>
-      <c r="D8">
-        <v>41500</v>
-      </c>
-      <c r="E8">
-        <v>3000</v>
-      </c>
-      <c r="F8">
-        <v>70000</v>
-      </c>
-      <c r="G8">
-        <v>44500</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>37500</v>
-      </c>
-      <c r="D9">
-        <v>41500</v>
-      </c>
-      <c r="E9">
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>1000</v>
+      </c>
+      <c r="C18">
+        <v>70000</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
+      </c>
+      <c r="E18">
         <v>2000</v>
       </c>
-      <c r="F9">
-        <v>70000</v>
-      </c>
-      <c r="G9">
-        <v>81000</v>
-      </c>
-      <c r="H9">
-        <v>650</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>13000</v>
-      </c>
-      <c r="K9">
-        <v>200</v>
-      </c>
-      <c r="L9">
-        <v>81000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>37500</v>
-      </c>
-      <c r="D10">
-        <v>41500</v>
-      </c>
-      <c r="E10">
-        <v>3000</v>
-      </c>
-      <c r="F10">
-        <v>70000</v>
-      </c>
-      <c r="G10">
-        <v>44500</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11">
-        <v>37500</v>
-      </c>
-      <c r="D11">
-        <v>41500</v>
-      </c>
-      <c r="E11">
-        <v>3000</v>
-      </c>
-      <c r="F11">
-        <v>70000</v>
-      </c>
-      <c r="G11">
-        <v>82000</v>
-      </c>
-      <c r="H11">
-        <v>4400</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>13000</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>82000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1011</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12">
-        <v>37500</v>
-      </c>
-      <c r="D12">
-        <v>41500</v>
-      </c>
-      <c r="E12">
-        <v>3000</v>
-      </c>
-      <c r="F12">
-        <v>70000</v>
-      </c>
-      <c r="G12">
-        <v>44500</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1012</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="C13">
-        <v>37500</v>
-      </c>
-      <c r="D13">
-        <v>41500</v>
-      </c>
-      <c r="E13">
-        <v>3000</v>
-      </c>
-      <c r="F13">
-        <v>70000</v>
-      </c>
-      <c r="G13">
-        <v>82000</v>
-      </c>
-      <c r="H13">
-        <v>3950</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>82000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1013</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14">
-        <v>37500</v>
-      </c>
-      <c r="D14">
-        <v>41500</v>
-      </c>
-      <c r="E14">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>70000</v>
+      </c>
+      <c r="D19">
         <v>2000</v>
       </c>
-      <c r="F14">
-        <v>70000</v>
-      </c>
-      <c r="G14">
-        <v>81000</v>
-      </c>
-      <c r="H14">
-        <v>287</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>81000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15">
-        <v>37500</v>
-      </c>
-      <c r="D15">
-        <v>41500</v>
-      </c>
-      <c r="E15">
-        <v>3000</v>
-      </c>
-      <c r="F15">
-        <v>70000</v>
-      </c>
-      <c r="G15">
-        <v>82000</v>
-      </c>
-      <c r="H15">
-        <v>1250</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>82000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1015</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16">
-        <v>37500</v>
-      </c>
-      <c r="D16">
-        <v>27000</v>
-      </c>
-      <c r="E16">
-        <v>3000</v>
-      </c>
-      <c r="F16">
-        <v>70000</v>
-      </c>
-      <c r="G16">
-        <v>30000</v>
-      </c>
-      <c r="H16">
+      <c r="E19">
         <v>2000</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1016</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17">
-        <v>37500</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>70000</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>2000</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1017</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18">
-        <v>37500</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>1000</v>
-      </c>
-      <c r="F18">
-        <v>70000</v>
-      </c>
-      <c r="G18">
-        <v>1000</v>
-      </c>
-      <c r="H18">
-        <v>2000</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>1000</v>
+      <c r="F19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1271,7 +1271,7 @@
         <v>70000</v>
       </c>
       <c r="D19">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Benefit_gain</t>
+  </si>
+  <si>
+    <t>expenditure</t>
   </si>
   <si>
     <t>Geetu Bekela</t>
@@ -897,10 +900,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -919,10 +922,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>3000</v>
@@ -939,10 +945,13 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>3000</v>
@@ -959,10 +968,13 @@
       <c r="F3">
         <v>13000</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>3000</v>
@@ -979,10 +991,13 @@
       <c r="F4">
         <v>13000</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>2000</v>
@@ -999,10 +1014,13 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>4000</v>
@@ -1019,10 +1037,13 @@
       <c r="F6">
         <v>13000</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>2000</v>
@@ -1039,10 +1060,13 @@
       <c r="F7">
         <v>13000</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>3000</v>
@@ -1059,10 +1083,13 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>2000</v>
@@ -1079,10 +1106,13 @@
       <c r="F9">
         <v>13000</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>3000</v>
@@ -1099,10 +1129,13 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>3000</v>
@@ -1119,10 +1152,13 @@
       <c r="F11">
         <v>13000</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>3000</v>
@@ -1139,10 +1175,13 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3000</v>
@@ -1159,10 +1198,13 @@
       <c r="F13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>2000</v>
@@ -1179,10 +1221,13 @@
       <c r="F14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>3000</v>
@@ -1199,10 +1244,13 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>3000</v>
@@ -1219,19 +1267,22 @@
       <c r="F16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C17">
         <v>70000</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E17">
         <v>2000</v>
@@ -1239,10 +1290,13 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>1000</v>
@@ -1259,10 +1313,13 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1277,6 +1334,9 @@
         <v>2000</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -93,7 +93,10 @@
     <t>Naggasaa Dheeressaa</t>
   </si>
   <si>
-    <t>Bacha ifa</t>
+    <t>Baacaa Ifaa</t>
+  </si>
+  <si>
+    <t>Nabiyat Habtewold</t>
   </si>
 </sst>
 </file>
@@ -900,8 +903,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1337,6 +1343,29 @@
         <v>0</v>
       </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>70000</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>2000</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6660"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -97,6 +97,15 @@
   </si>
   <si>
     <t>Nabiyat Habtewold</t>
+  </si>
+  <si>
+    <t>Chaluma Uma</t>
+  </si>
+  <si>
+    <t>Ababa Fayisa</t>
+  </si>
+  <si>
+    <t>Worku Bekele</t>
   </si>
 </sst>
 </file>
@@ -903,10 +912,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1369,6 +1384,75 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>70000</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>2000</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>70000</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>2000</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>70000</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>2000</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1171,7 +1171,7 @@
         <v>4400</v>
       </c>
       <c r="F11">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="G11">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -975,7 +975,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C3">
         <v>70000</v>
@@ -998,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C4">
         <v>70000</v>
@@ -1044,7 +1044,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C6">
         <v>70000</v>
@@ -1113,7 +1113,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C9">
         <v>70000</v>
@@ -1159,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C11">
         <v>70000</v>
@@ -1182,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C12">
         <v>70000</v>
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C14">
         <v>70000</v>
@@ -1251,7 +1251,7 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C15">
         <v>70000</v>
@@ -1280,7 +1280,7 @@
         <v>70000</v>
       </c>
       <c r="D16">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E16">
         <v>2000</v>
@@ -1297,13 +1297,13 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C17">
         <v>70000</v>
       </c>
       <c r="D17">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="E17">
         <v>2000</v>
@@ -1320,7 +1320,7 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C18">
         <v>70000</v>
@@ -1366,7 +1366,7 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C20">
         <v>70000</v>
@@ -1435,7 +1435,7 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C23">
         <v>70000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1191,7 +1191,7 @@
         <v>44500</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1389,7 +1389,7 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C21">
         <v>70000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -589,8 +589,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1067,13 +1070,13 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C7">
         <v>70000</v>
       </c>
-      <c r="D7">
-        <v>43500</v>
+      <c r="D7" s="1">
+        <v>82500</v>
       </c>
       <c r="E7">
         <v>650</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -955,13 +955,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C2">
         <v>70000</v>
       </c>
-      <c r="D2">
-        <v>70000</v>
+      <c r="D2" s="1">
+        <v>71000</v>
       </c>
       <c r="E2">
         <v>242</v>
@@ -983,8 +983,8 @@
       <c r="C3">
         <v>70000</v>
       </c>
-      <c r="D3">
-        <v>82000</v>
+      <c r="D3" s="1">
+        <v>83000</v>
       </c>
       <c r="E3">
         <v>2400</v>
@@ -1006,8 +1006,8 @@
       <c r="C4">
         <v>70000</v>
       </c>
-      <c r="D4">
-        <v>46500</v>
+      <c r="D4" s="1">
+        <v>86500</v>
       </c>
       <c r="E4">
         <v>650</v>
@@ -1029,7 +1029,7 @@
       <c r="C5">
         <v>70000</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>43500</v>
       </c>
       <c r="E5">
@@ -1052,8 +1052,8 @@
       <c r="C6">
         <v>70000</v>
       </c>
-      <c r="D6">
-        <v>45500</v>
+      <c r="D6" s="1">
+        <v>47500</v>
       </c>
       <c r="E6">
         <v>892</v>
@@ -1076,7 +1076,7 @@
         <v>70000</v>
       </c>
       <c r="D7" s="1">
-        <v>82500</v>
+        <v>83500</v>
       </c>
       <c r="E7">
         <v>650</v>
@@ -1093,13 +1093,13 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C8">
         <v>70000</v>
       </c>
-      <c r="D8">
-        <v>44500</v>
+      <c r="D8" s="1">
+        <v>45500</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1121,8 +1121,8 @@
       <c r="C9">
         <v>70000</v>
       </c>
-      <c r="D9">
-        <v>81000</v>
+      <c r="D9" s="1">
+        <v>82000</v>
       </c>
       <c r="E9">
         <v>650</v>
@@ -1139,13 +1139,13 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C10">
         <v>70000</v>
       </c>
-      <c r="D10">
-        <v>44500</v>
+      <c r="D10" s="1">
+        <v>45500</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1167,8 +1167,8 @@
       <c r="C11">
         <v>70000</v>
       </c>
-      <c r="D11">
-        <v>82000</v>
+      <c r="D11" s="1">
+        <v>83000</v>
       </c>
       <c r="E11">
         <v>4400</v>
@@ -1190,8 +1190,8 @@
       <c r="C12">
         <v>70000</v>
       </c>
-      <c r="D12">
-        <v>44500</v>
+      <c r="D12" s="1">
+        <v>45500</v>
       </c>
       <c r="E12">
         <v>700</v>
@@ -1208,13 +1208,13 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C13">
         <v>70000</v>
       </c>
-      <c r="D13">
-        <v>82000</v>
+      <c r="D13" s="1">
+        <v>83000</v>
       </c>
       <c r="E13">
         <v>3950</v>
@@ -1236,8 +1236,8 @@
       <c r="C14">
         <v>70000</v>
       </c>
-      <c r="D14">
-        <v>81000</v>
+      <c r="D14" s="1">
+        <v>82000</v>
       </c>
       <c r="E14">
         <v>287</v>
@@ -1259,8 +1259,8 @@
       <c r="C15">
         <v>70000</v>
       </c>
-      <c r="D15">
-        <v>82000</v>
+      <c r="D15" s="1">
+        <v>83000</v>
       </c>
       <c r="E15">
         <v>1250</v>
@@ -1282,8 +1282,8 @@
       <c r="C16">
         <v>70000</v>
       </c>
-      <c r="D16">
-        <v>40000</v>
+      <c r="D16" s="1">
+        <v>43000</v>
       </c>
       <c r="E16">
         <v>2000</v>
@@ -1305,8 +1305,8 @@
       <c r="C17">
         <v>70000</v>
       </c>
-      <c r="D17">
-        <v>28000</v>
+      <c r="D17" s="1">
+        <v>30000</v>
       </c>
       <c r="E17">
         <v>2000</v>
@@ -1328,8 +1328,8 @@
       <c r="C18">
         <v>70000</v>
       </c>
-      <c r="D18">
-        <v>1000</v>
+      <c r="D18" s="1">
+        <v>42000</v>
       </c>
       <c r="E18">
         <v>2000</v>
@@ -1351,7 +1351,7 @@
       <c r="C19">
         <v>70000</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19">
@@ -1374,8 +1374,8 @@
       <c r="C20">
         <v>70000</v>
       </c>
-      <c r="D20">
-        <v>0</v>
+      <c r="D20" s="1">
+        <v>1000</v>
       </c>
       <c r="E20">
         <v>2000</v>
@@ -1397,8 +1397,8 @@
       <c r="C21">
         <v>70000</v>
       </c>
-      <c r="D21">
-        <v>0</v>
+      <c r="D21" s="1">
+        <v>1000</v>
       </c>
       <c r="E21">
         <v>2000</v>
@@ -1415,13 +1415,13 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C22">
         <v>70000</v>
       </c>
-      <c r="D22">
-        <v>0</v>
+      <c r="D22" s="1">
+        <v>1000</v>
       </c>
       <c r="E22">
         <v>2000</v>
@@ -1443,8 +1443,8 @@
       <c r="C23">
         <v>70000</v>
       </c>
-      <c r="D23">
-        <v>0</v>
+      <c r="D23" s="1">
+        <v>1000</v>
       </c>
       <c r="E23">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Name</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Worku Bekele</t>
+  </si>
+  <si>
+    <t>Milkesa Gebre</t>
   </si>
 </sst>
 </file>
@@ -915,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -1456,6 +1459,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>70000</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>2000</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1378,7 +1378,7 @@
         <v>70000</v>
       </c>
       <c r="D20" s="1">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="E20">
         <v>2000</v>
@@ -1464,13 +1464,13 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C24">
         <v>70000</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="E24">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -966,10 +966,10 @@
       <c r="D2" s="1">
         <v>71000</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>242</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2">
@@ -989,11 +989,11 @@
       <c r="D3" s="1">
         <v>83000</v>
       </c>
-      <c r="E3">
-        <v>2400</v>
-      </c>
-      <c r="F3">
-        <v>13000</v>
+      <c r="E3" s="1">
+        <v>2750</v>
+      </c>
+      <c r="F3" s="1">
+        <v>20000</v>
       </c>
       <c r="G3">
         <v>1950</v>
@@ -1012,10 +1012,10 @@
       <c r="D4" s="1">
         <v>86500</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>650</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>13000</v>
       </c>
       <c r="G4">
@@ -1035,10 +1035,10 @@
       <c r="D5" s="1">
         <v>43500</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5">
@@ -1058,10 +1058,10 @@
       <c r="D6" s="1">
         <v>47500</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>892</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>13000</v>
       </c>
       <c r="G6">
@@ -1081,10 +1081,10 @@
       <c r="D7" s="1">
         <v>83500</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>650</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>13000</v>
       </c>
       <c r="G7">
@@ -1104,10 +1104,10 @@
       <c r="D8" s="1">
         <v>45500</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8">
@@ -1127,10 +1127,10 @@
       <c r="D9" s="1">
         <v>82000</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>650</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>13000</v>
       </c>
       <c r="G9">
@@ -1150,10 +1150,10 @@
       <c r="D10" s="1">
         <v>45500</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10">
@@ -1173,10 +1173,10 @@
       <c r="D11" s="1">
         <v>83000</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>4400</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>16000</v>
       </c>
       <c r="G11">
@@ -1196,10 +1196,10 @@
       <c r="D12" s="1">
         <v>45500</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>700</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12">
@@ -1219,10 +1219,10 @@
       <c r="D13" s="1">
         <v>83000</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>3950</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13">
@@ -1242,11 +1242,11 @@
       <c r="D14" s="1">
         <v>82000</v>
       </c>
-      <c r="E14">
-        <v>287</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
+      <c r="E14" s="1">
+        <v>637</v>
+      </c>
+      <c r="F14" s="1">
+        <v>7000</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1265,10 +1265,10 @@
       <c r="D15" s="1">
         <v>83000</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>1250</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15">
@@ -1288,10 +1288,10 @@
       <c r="D16" s="1">
         <v>43000</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>2000</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16">
@@ -1311,10 +1311,10 @@
       <c r="D17" s="1">
         <v>30000</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>2000</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17">
@@ -1334,10 +1334,10 @@
       <c r="D18" s="1">
         <v>42000</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>2000</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18">
@@ -1357,10 +1357,10 @@
       <c r="D19" s="1">
         <v>0</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>2000</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19">
@@ -1380,10 +1380,10 @@
       <c r="D20" s="1">
         <v>15000</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>2000</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20">
@@ -1403,10 +1403,10 @@
       <c r="D21" s="1">
         <v>1000</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>2000</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21">
@@ -1426,10 +1426,10 @@
       <c r="D22" s="1">
         <v>1000</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>2000</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22">
@@ -1449,10 +1449,10 @@
       <c r="D23" s="1">
         <v>1000</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>2000</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23">
@@ -1472,10 +1472,10 @@
       <c r="D24" s="1">
         <v>41000</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>2000</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24">

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Milkesa Gebre</t>
+  </si>
+  <si>
+    <t>Worku Guta</t>
   </si>
 </sst>
 </file>
@@ -918,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -1482,6 +1485,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C25">
+        <v>70000</v>
+      </c>
+      <c r="D25" s="1">
+        <v>97000</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1496,7 +1496,7 @@
         <v>70000</v>
       </c>
       <c r="D25" s="1">
-        <v>97000</v>
+        <v>98000</v>
       </c>
       <c r="E25" s="1">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>business_date</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Q1_plan</t>
+  </si>
+  <si>
+    <t>Q1_achievement</t>
+  </si>
+  <si>
     <t>Monthly_payment_Q2</t>
   </si>
   <si>
@@ -36,10 +48,16 @@
     <t>fee_charge</t>
   </si>
   <si>
+    <t>volentary_saving</t>
+  </si>
+  <si>
     <t>Benefit_gain</t>
   </si>
   <si>
-    <t>expenditure</t>
+    <t>Expenditure</t>
+  </si>
+  <si>
+    <t>total_payr</t>
   </si>
   <si>
     <t>Geetu Bekela</t>
@@ -66,7 +84,7 @@
     <t>Lami Diro</t>
   </si>
   <si>
-    <t>Mokenon Bayena</t>
+    <t>Boki Bayena</t>
   </si>
   <si>
     <t>Salamon Zarihun</t>
@@ -84,7 +102,7 @@
     <t>Barsisa Merga</t>
   </si>
   <si>
-    <t>Gemechu Asefa</t>
+    <t>Abera Asefa</t>
   </si>
   <si>
     <t>Alamuu Guutaa</t>
@@ -597,9 +615,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -921,19 +937,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -955,556 +965,1006 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>45885</v>
+      </c>
       <c r="B2">
+        <v>1001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>37500</v>
+      </c>
+      <c r="E2">
+        <v>41500</v>
+      </c>
+      <c r="F2">
+        <v>3000</v>
+      </c>
+      <c r="G2">
+        <v>70000</v>
+      </c>
+      <c r="H2">
+        <v>70000</v>
+      </c>
+      <c r="I2">
+        <v>242</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45826</v>
+      </c>
+      <c r="B3">
+        <v>1002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <v>37500</v>
+      </c>
+      <c r="E3">
+        <v>41500</v>
+      </c>
+      <c r="F3">
+        <v>3000</v>
+      </c>
+      <c r="G3">
+        <v>70000</v>
+      </c>
+      <c r="H3">
+        <v>82000</v>
+      </c>
+      <c r="I3">
+        <v>2750</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>20250</v>
+      </c>
+      <c r="L3">
+        <v>1950</v>
+      </c>
+      <c r="M3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45845</v>
+      </c>
+      <c r="B4">
+        <v>1003</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>37500</v>
+      </c>
+      <c r="E4">
+        <v>41500</v>
+      </c>
+      <c r="F4">
+        <v>3000</v>
+      </c>
+      <c r="G4">
+        <v>70000</v>
+      </c>
+      <c r="H4">
+        <v>85500</v>
+      </c>
+      <c r="I4">
+        <v>650</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>13000</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45826</v>
+      </c>
+      <c r="B5">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>37500</v>
+      </c>
+      <c r="E5">
+        <v>41500</v>
+      </c>
+      <c r="F5">
+        <v>2000</v>
+      </c>
+      <c r="G5">
+        <v>70000</v>
+      </c>
+      <c r="H5">
+        <v>43500</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>6900</v>
+      </c>
+      <c r="M5">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45885</v>
+      </c>
+      <c r="B6">
+        <v>1005</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>37500</v>
+      </c>
+      <c r="E6">
+        <v>41500</v>
+      </c>
+      <c r="F6">
         <v>4000</v>
       </c>
-      <c r="C2">
-        <v>70000</v>
-      </c>
-      <c r="D2" s="1">
-        <v>71000</v>
-      </c>
-      <c r="E2" s="1">
-        <v>242</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>4000</v>
-      </c>
-      <c r="C3">
-        <v>70000</v>
-      </c>
-      <c r="D3" s="1">
-        <v>83000</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2750</v>
-      </c>
-      <c r="F3" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G3">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>4000</v>
-      </c>
-      <c r="C4">
-        <v>70000</v>
-      </c>
-      <c r="D4" s="1">
-        <v>86500</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="G6">
+        <v>70000</v>
+      </c>
+      <c r="H6">
+        <v>46500</v>
+      </c>
+      <c r="I6">
+        <v>892</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>13000</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45826</v>
+      </c>
+      <c r="B7">
+        <v>1006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>37500</v>
+      </c>
+      <c r="E7">
+        <v>41500</v>
+      </c>
+      <c r="F7">
+        <v>3000</v>
+      </c>
+      <c r="G7">
+        <v>70000</v>
+      </c>
+      <c r="H7">
+        <v>82500</v>
+      </c>
+      <c r="I7">
         <v>650</v>
       </c>
-      <c r="F4" s="1">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>13100</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45826</v>
+      </c>
+      <c r="B8">
+        <v>1007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>37500</v>
+      </c>
+      <c r="E8">
+        <v>41500</v>
+      </c>
+      <c r="F8">
+        <v>3000</v>
+      </c>
+      <c r="G8">
+        <v>70000</v>
+      </c>
+      <c r="H8">
+        <v>44500</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45826</v>
+      </c>
+      <c r="B9">
+        <v>1008</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>37500</v>
+      </c>
+      <c r="E9">
+        <v>41500</v>
+      </c>
+      <c r="F9">
+        <v>2000</v>
+      </c>
+      <c r="G9">
+        <v>70000</v>
+      </c>
+      <c r="H9">
+        <v>81000</v>
+      </c>
+      <c r="I9">
+        <v>650</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>13000</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
+      <c r="L9">
+        <v>200</v>
+      </c>
+      <c r="M9">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45849</v>
+      </c>
+      <c r="B10">
+        <v>1009</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>37500</v>
+      </c>
+      <c r="E10">
+        <v>41500</v>
+      </c>
+      <c r="F10">
+        <v>3000</v>
+      </c>
+      <c r="G10">
+        <v>70000</v>
+      </c>
+      <c r="H10">
+        <v>44500</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>45844</v>
+      </c>
+      <c r="B11">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>37500</v>
+      </c>
+      <c r="E11">
+        <v>41500</v>
+      </c>
+      <c r="F11">
+        <v>3000</v>
+      </c>
+      <c r="G11">
+        <v>70000</v>
+      </c>
+      <c r="H11">
+        <v>82000</v>
+      </c>
+      <c r="I11">
+        <v>4400</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>17000</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12">
+        <v>37500</v>
+      </c>
+      <c r="E12">
+        <v>41500</v>
+      </c>
+      <c r="F12">
+        <v>3000</v>
+      </c>
+      <c r="G12">
+        <v>70000</v>
+      </c>
+      <c r="H12">
+        <v>44500</v>
+      </c>
+      <c r="I12">
+        <v>700</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45880</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>37500</v>
+      </c>
+      <c r="E13">
+        <v>41500</v>
+      </c>
+      <c r="F13">
+        <v>3000</v>
+      </c>
+      <c r="G13">
+        <v>70000</v>
+      </c>
+      <c r="H13">
+        <v>82000</v>
+      </c>
+      <c r="I13">
+        <v>3950</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45893</v>
+      </c>
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>37500</v>
+      </c>
+      <c r="E14">
+        <v>41500</v>
+      </c>
+      <c r="F14">
         <v>2000</v>
       </c>
-      <c r="C5">
-        <v>70000</v>
-      </c>
-      <c r="D5" s="1">
-        <v>43500</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>6900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>5000</v>
-      </c>
-      <c r="C6">
-        <v>70000</v>
-      </c>
-      <c r="D6" s="1">
-        <v>47500</v>
-      </c>
-      <c r="E6" s="1">
-        <v>892</v>
-      </c>
-      <c r="F6" s="1">
-        <v>13000</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>4000</v>
-      </c>
-      <c r="C7">
-        <v>70000</v>
-      </c>
-      <c r="D7" s="1">
-        <v>83500</v>
-      </c>
-      <c r="E7" s="1">
-        <v>650</v>
-      </c>
-      <c r="F7" s="1">
-        <v>13000</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>4000</v>
-      </c>
-      <c r="C8">
-        <v>70000</v>
-      </c>
-      <c r="D8" s="1">
-        <v>45500</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
+      <c r="G14">
+        <v>70000</v>
+      </c>
+      <c r="H14">
+        <v>81000</v>
+      </c>
+      <c r="I14">
+        <v>637</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>7000</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45877</v>
+      </c>
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>37500</v>
+      </c>
+      <c r="E15">
+        <v>41500</v>
+      </c>
+      <c r="F15">
         <v>3000</v>
       </c>
-      <c r="C9">
-        <v>70000</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="G15">
+        <v>70000</v>
+      </c>
+      <c r="H15">
         <v>82000</v>
       </c>
-      <c r="E9" s="1">
-        <v>650</v>
-      </c>
-      <c r="F9" s="1">
-        <v>13000</v>
-      </c>
-      <c r="G9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>4000</v>
-      </c>
-      <c r="C10">
-        <v>70000</v>
-      </c>
-      <c r="D10" s="1">
-        <v>45500</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>4000</v>
-      </c>
-      <c r="C11">
-        <v>70000</v>
-      </c>
-      <c r="D11" s="1">
-        <v>83000</v>
-      </c>
-      <c r="E11" s="1">
-        <v>4400</v>
-      </c>
-      <c r="F11" s="1">
-        <v>16000</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>4000</v>
-      </c>
-      <c r="C12">
-        <v>70000</v>
-      </c>
-      <c r="D12" s="1">
-        <v>45500</v>
-      </c>
-      <c r="E12" s="1">
-        <v>700</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>4000</v>
-      </c>
-      <c r="C13">
-        <v>70000</v>
-      </c>
-      <c r="D13" s="1">
-        <v>83000</v>
-      </c>
-      <c r="E13" s="1">
-        <v>3950</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>3000</v>
-      </c>
-      <c r="C14">
-        <v>70000</v>
-      </c>
-      <c r="D14" s="1">
-        <v>82000</v>
-      </c>
-      <c r="E14" s="1">
-        <v>637</v>
-      </c>
-      <c r="F14" s="1">
-        <v>7000</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>4000</v>
-      </c>
-      <c r="C15">
-        <v>70000</v>
-      </c>
-      <c r="D15" s="1">
-        <v>83000</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="I15">
         <v>1250</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>21</v>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45977</v>
       </c>
       <c r="B16">
-        <v>3000</v>
-      </c>
-      <c r="C16">
-        <v>70000</v>
-      </c>
-      <c r="D16" s="1">
-        <v>43000</v>
-      </c>
-      <c r="E16" s="1">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16">
+        <v>37500</v>
+      </c>
+      <c r="E16">
+        <v>36000</v>
+      </c>
+      <c r="F16">
         <v>2000</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
+        <v>70000</v>
+      </c>
+      <c r="H16">
+        <v>42000</v>
+      </c>
+      <c r="I16">
+        <v>2000</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45997</v>
       </c>
       <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17">
+        <v>37500</v>
+      </c>
+      <c r="E17">
+        <v>14000</v>
+      </c>
+      <c r="F17">
+        <v>1000</v>
+      </c>
+      <c r="G17">
+        <v>70000</v>
+      </c>
+      <c r="H17">
+        <v>29000</v>
+      </c>
+      <c r="I17">
         <v>2000</v>
       </c>
-      <c r="C17">
-        <v>70000</v>
-      </c>
-      <c r="D17" s="1">
-        <v>30000</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46004</v>
+      </c>
+      <c r="B18">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>37500</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1000</v>
+      </c>
+      <c r="G18">
+        <v>70000</v>
+      </c>
+      <c r="H18">
+        <v>41000</v>
+      </c>
+      <c r="I18">
         <v>2000</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B19">
+        <v>1018</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>37500</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>70000</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>2000</v>
       </c>
-      <c r="C18">
-        <v>70000</v>
-      </c>
-      <c r="D18" s="1">
-        <v>42000</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B20">
+        <v>1019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>37500</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>70000</v>
+      </c>
+      <c r="H20">
+        <v>14000</v>
+      </c>
+      <c r="I20">
         <v>2000</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>70000</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B21">
+        <v>1020</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>37500</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>70000</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>2000</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20">
-        <v>1000</v>
-      </c>
-      <c r="C20">
-        <v>70000</v>
-      </c>
-      <c r="D20" s="1">
-        <v>15000</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B22">
+        <v>1021</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>37500</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>70000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>2000</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
-        <v>1000</v>
-      </c>
-      <c r="C21">
-        <v>70000</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B23">
+        <v>1022</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23">
+        <v>37500</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>70000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>2000</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22">
-        <v>1000</v>
-      </c>
-      <c r="C22">
-        <v>70000</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B24">
+        <v>1023</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>37500</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>70000</v>
+      </c>
+      <c r="H24">
+        <v>40000</v>
+      </c>
+      <c r="I24">
         <v>2000</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23">
-        <v>1000</v>
-      </c>
-      <c r="C23">
-        <v>70000</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B25">
+        <v>1024</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25">
+        <v>37500</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>70000</v>
+      </c>
+      <c r="H25">
+        <v>97000</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>2000</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24">
-        <v>1000</v>
-      </c>
-      <c r="C24">
-        <v>70000</v>
-      </c>
-      <c r="D24" s="1">
-        <v>41000</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1000</v>
-      </c>
-      <c r="C25">
-        <v>70000</v>
-      </c>
-      <c r="D25" s="1">
-        <v>98000</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -941,6 +941,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1739,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G20">
         <v>70000</v>
@@ -1780,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G21">
         <v>70000</v>
@@ -1821,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G22">
         <v>70000</v>
@@ -1862,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G23">
         <v>70000</v>
@@ -1903,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G24">
         <v>70000</v>
@@ -1944,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G25">
         <v>70000</v>
@@ -1953,10 +1954,10 @@
         <v>97000</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J25">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6660"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -941,7 +941,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1008,7 +1007,7 @@
         <v>70000</v>
       </c>
       <c r="H2">
-        <v>70000</v>
+        <v>71000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1049,7 +1048,7 @@
         <v>70000</v>
       </c>
       <c r="H3">
-        <v>82000</v>
+        <v>83000</v>
       </c>
       <c r="I3">
         <v>2750</v>
@@ -1090,7 +1089,7 @@
         <v>70000</v>
       </c>
       <c r="H4">
-        <v>85500</v>
+        <v>86500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1172,7 +1171,7 @@
         <v>70000</v>
       </c>
       <c r="H6">
-        <v>46500</v>
+        <v>47500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1213,7 +1212,7 @@
         <v>70000</v>
       </c>
       <c r="H7">
-        <v>82500</v>
+        <v>83500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1254,7 +1253,7 @@
         <v>70000</v>
       </c>
       <c r="H8">
-        <v>44500</v>
+        <v>45500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1295,7 +1294,7 @@
         <v>70000</v>
       </c>
       <c r="H9">
-        <v>81000</v>
+        <v>82000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1336,7 +1335,7 @@
         <v>70000</v>
       </c>
       <c r="H10">
-        <v>44500</v>
+        <v>45500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1377,7 +1376,7 @@
         <v>70000</v>
       </c>
       <c r="H11">
-        <v>82000</v>
+        <v>83000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1418,7 +1417,7 @@
         <v>70000</v>
       </c>
       <c r="H12">
-        <v>44500</v>
+        <v>45500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1459,7 +1458,7 @@
         <v>70000</v>
       </c>
       <c r="H13">
-        <v>82000</v>
+        <v>83000</v>
       </c>
       <c r="I13">
         <v>3950</v>
@@ -1500,7 +1499,7 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <v>81000</v>
+        <v>82000</v>
       </c>
       <c r="I14">
         <v>637</v>
@@ -1541,7 +1540,7 @@
         <v>70000</v>
       </c>
       <c r="H15">
-        <v>82000</v>
+        <v>83000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1582,7 +1581,7 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1623,7 +1622,7 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1664,7 +1663,7 @@
         <v>70000</v>
       </c>
       <c r="H18">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="I18">
         <v>2000</v>
@@ -1746,7 +1745,7 @@
         <v>70000</v>
       </c>
       <c r="H20">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1910,7 +1909,7 @@
         <v>70000</v>
       </c>
       <c r="H24">
-        <v>40000</v>
+        <v>41000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1951,7 +1950,7 @@
         <v>70000</v>
       </c>
       <c r="H25">
-        <v>97000</v>
+        <v>98000</v>
       </c>
       <c r="I25">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -1786,7 +1786,7 @@
         <v>70000</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1827,7 +1827,7 @@
         <v>70000</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1868,7 +1868,7 @@
         <v>70000</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I23">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>13000</v>
+        <v>15250</v>
       </c>
       <c r="L4">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="L15">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,7 +36,7 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q2</t>
+    <t>Monthly_payment_Q3</t>
   </si>
   <si>
     <t>Q2_plan</t>
@@ -941,6 +941,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1042,7 +1045,7 @@
         <v>41500</v>
       </c>
       <c r="F3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G3">
         <v>70000</v>
@@ -1057,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>20250</v>
+        <v>22500</v>
       </c>
       <c r="L3">
         <v>1950</v>
@@ -1083,7 +1086,7 @@
         <v>41500</v>
       </c>
       <c r="F4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G4">
         <v>70000</v>
@@ -1124,7 +1127,7 @@
         <v>41500</v>
       </c>
       <c r="F5">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G5">
         <v>70000</v>
@@ -1165,7 +1168,7 @@
         <v>41500</v>
       </c>
       <c r="F6">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G6">
         <v>70000</v>
@@ -1206,7 +1209,7 @@
         <v>41500</v>
       </c>
       <c r="F7">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G7">
         <v>70000</v>
@@ -1288,13 +1291,13 @@
         <v>41500</v>
       </c>
       <c r="F9">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G9">
         <v>70000</v>
       </c>
       <c r="H9">
-        <v>82000</v>
+        <v>91000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1370,7 +1373,7 @@
         <v>41500</v>
       </c>
       <c r="F11">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G11">
         <v>70000</v>
@@ -1411,7 +1414,7 @@
         <v>41500</v>
       </c>
       <c r="F12">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G12">
         <v>70000</v>
@@ -1426,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1452,7 +1455,7 @@
         <v>41500</v>
       </c>
       <c r="F13">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G13">
         <v>70000</v>
@@ -1493,7 +1496,7 @@
         <v>41500</v>
       </c>
       <c r="F14">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G14">
         <v>70000</v>
@@ -1534,7 +1537,7 @@
         <v>41500</v>
       </c>
       <c r="F15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G15">
         <v>70000</v>
@@ -1821,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G22">
         <v>70000</v>
@@ -1862,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G23">
         <v>70000</v>
@@ -1903,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G24">
         <v>70000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -941,6 +941,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -963,28 +964,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -995,7 +996,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1036,7 +1037,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1077,7 +1078,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1118,7 +1119,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1159,7 +1160,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1200,7 +1201,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1241,7 +1242,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1282,7 +1283,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1323,7 +1324,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1364,7 +1365,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1405,7 +1406,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1446,7 +1447,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1487,7 +1488,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1528,7 +1529,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1569,7 +1570,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1610,7 +1611,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1651,7 +1652,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1692,7 +1693,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1733,7 +1734,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1774,7 +1775,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1815,7 +1816,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1856,7 +1857,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1897,7 +1898,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1938,7 +1939,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -941,10 +941,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -964,28 +960,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -996,7 +992,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1037,7 +1033,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1078,7 +1074,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1119,7 +1115,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1160,7 +1156,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1184,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>13000</v>
+        <v>15250</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1201,7 +1197,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1242,7 +1238,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1266,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1283,7 +1279,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1324,7 +1320,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1365,7 +1361,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1389,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>17000</v>
+        <v>19250</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1406,7 +1402,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1447,7 +1443,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1488,7 +1484,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1512,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>7000</v>
+        <v>9250</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1529,7 +1525,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1570,7 +1566,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1611,7 +1607,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1652,7 +1648,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1693,7 +1689,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1734,7 +1730,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1775,7 +1771,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1816,7 +1812,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1857,7 +1853,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1898,7 +1894,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1939,7 +1935,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -941,6 +941,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -960,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -992,7 +993,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1033,7 +1034,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1074,7 +1075,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1115,7 +1116,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1156,7 +1157,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1197,7 +1198,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1238,7 +1239,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1279,7 +1280,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1320,7 +1321,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1361,7 +1362,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1402,7 +1403,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1443,7 +1444,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1484,7 +1485,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1525,7 +1526,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1566,7 +1567,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1607,7 +1608,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1648,7 +1649,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1689,7 +1690,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1730,7 +1731,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1771,7 +1772,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1812,7 +1813,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1853,7 +1854,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1894,7 +1895,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1935,7 +1936,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -941,7 +941,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -961,28 +967,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -993,7 +999,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1002,7 +1008,7 @@
         <v>41500</v>
       </c>
       <c r="F2">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G2">
         <v>70000</v>
@@ -1034,7 +1040,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1075,7 +1081,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1116,7 +1122,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1157,7 +1163,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1198,7 +1204,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1239,7 +1245,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1248,7 +1254,7 @@
         <v>41500</v>
       </c>
       <c r="F8">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G8">
         <v>70000</v>
@@ -1280,7 +1286,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1321,7 +1327,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1362,7 +1368,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1403,7 +1409,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1444,7 +1450,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1485,7 +1491,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1526,7 +1532,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1567,7 +1573,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1608,7 +1614,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1649,7 +1655,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1690,7 +1696,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1731,7 +1737,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1772,7 +1778,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1813,7 +1819,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1854,7 +1860,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1895,7 +1901,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1936,7 +1942,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -944,6 +944,7 @@
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -967,28 +968,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -999,7 +1000,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1040,7 +1041,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1081,7 +1082,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1122,7 +1123,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1163,7 +1164,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1204,7 +1205,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1245,7 +1246,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1286,7 +1287,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1327,7 +1328,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1368,7 +1369,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1409,7 +1410,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1450,7 +1451,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1491,7 +1492,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1532,7 +1533,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1573,7 +1574,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1614,7 +1615,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1655,7 +1656,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1696,7 +1697,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1737,7 +1738,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1778,7 +1779,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1819,7 +1820,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1860,7 +1861,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1901,7 +1902,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1942,7 +1943,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1015,7 +1015,7 @@
         <v>70000</v>
       </c>
       <c r="H2">
-        <v>71000</v>
+        <v>72000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1056,7 +1056,7 @@
         <v>70000</v>
       </c>
       <c r="H3">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="I3">
         <v>2750</v>
@@ -1097,7 +1097,7 @@
         <v>70000</v>
       </c>
       <c r="H4">
-        <v>86500</v>
+        <v>87500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1138,7 +1138,7 @@
         <v>70000</v>
       </c>
       <c r="H5">
-        <v>43500</v>
+        <v>44500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>70000</v>
       </c>
       <c r="H6">
-        <v>47500</v>
+        <v>48500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1220,7 +1220,7 @@
         <v>70000</v>
       </c>
       <c r="H7">
-        <v>83500</v>
+        <v>84500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1261,7 +1261,7 @@
         <v>70000</v>
       </c>
       <c r="H8">
-        <v>45500</v>
+        <v>46500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>70000</v>
       </c>
       <c r="H11">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1425,7 +1425,7 @@
         <v>70000</v>
       </c>
       <c r="H12">
-        <v>45500</v>
+        <v>46500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1466,7 +1466,7 @@
         <v>70000</v>
       </c>
       <c r="H13">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="I13">
         <v>3950</v>
@@ -1507,7 +1507,7 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <v>82000</v>
+        <v>83000</v>
       </c>
       <c r="I14">
         <v>637</v>
@@ -1548,7 +1548,7 @@
         <v>70000</v>
       </c>
       <c r="H15">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1835,7 +1835,7 @@
         <v>70000</v>
       </c>
       <c r="H22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1876,7 +1876,7 @@
         <v>70000</v>
       </c>
       <c r="H23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1917,7 +1917,7 @@
         <v>70000</v>
       </c>
       <c r="H24">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="I24">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1583,13 +1583,13 @@
         <v>36000</v>
       </c>
       <c r="F16">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G16">
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>43000</v>
+        <v>52000</v>
       </c>
       <c r="I16">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -945,6 +945,7 @@
     <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1589,7 +1590,7 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="I16">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1338,13 +1338,13 @@
         <v>41500</v>
       </c>
       <c r="F10">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G10">
         <v>70000</v>
       </c>
       <c r="H10">
-        <v>45500</v>
+        <v>46500</v>
       </c>
       <c r="I10">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G18">
         <v>70000</v>
       </c>
       <c r="H18">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I18">
         <v>2000</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G20">
         <v>70000</v>
       </c>
       <c r="H20">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="I20">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1508,7 +1508,7 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="I14">
         <v>637</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -946,6 +946,7 @@
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1675,7 +1676,7 @@
         <v>43000</v>
       </c>
       <c r="I18">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="J18">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1682,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1790,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G21">
         <v>70000</v>
       </c>
       <c r="H21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I21">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1954,13 +1954,13 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G25">
         <v>70000</v>
       </c>
       <c r="H25">
-        <v>98000</v>
+        <v>99000</v>
       </c>
       <c r="I25">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1626,13 +1626,13 @@
         <v>14000</v>
       </c>
       <c r="F17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G17">
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>30000</v>
+        <v>420000</v>
       </c>
       <c r="I17">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1632,7 +1632,7 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>420000</v>
+        <v>42000</v>
       </c>
       <c r="I17">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1632,7 +1632,7 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I17">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="L24">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -945,6 +945,7 @@
     <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
@@ -970,28 +971,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1002,7 +1003,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1017,7 +1018,7 @@
         <v>70000</v>
       </c>
       <c r="H2">
-        <v>72000</v>
+        <v>71000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1043,7 +1044,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1058,16 +1059,16 @@
         <v>70000</v>
       </c>
       <c r="H3">
-        <v>84000</v>
+        <v>131525</v>
       </c>
       <c r="I3">
-        <v>2750</v>
+        <v>1400</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>22500</v>
+        <v>23625</v>
       </c>
       <c r="L3">
         <v>1950</v>
@@ -1084,7 +1085,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1099,7 +1100,7 @@
         <v>70000</v>
       </c>
       <c r="H4">
-        <v>87500</v>
+        <v>96500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1125,7 +1126,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1140,7 +1141,7 @@
         <v>70000</v>
       </c>
       <c r="H5">
-        <v>44500</v>
+        <v>43500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1166,7 +1167,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1181,7 +1182,7 @@
         <v>70000</v>
       </c>
       <c r="H6">
-        <v>48500</v>
+        <v>47500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1207,7 +1208,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1222,7 +1223,7 @@
         <v>70000</v>
       </c>
       <c r="H7">
-        <v>84500</v>
+        <v>83500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1231,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>13100</v>
+        <v>15350</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1248,7 +1249,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1263,7 +1264,7 @@
         <v>70000</v>
       </c>
       <c r="H8">
-        <v>46500</v>
+        <v>45500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1289,7 +1290,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1304,7 +1305,7 @@
         <v>70000</v>
       </c>
       <c r="H9">
-        <v>91000</v>
+        <v>110000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1313,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>13000</v>
+        <v>15250</v>
       </c>
       <c r="L9">
         <v>200</v>
@@ -1330,7 +1331,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1345,7 +1346,7 @@
         <v>70000</v>
       </c>
       <c r="H10">
-        <v>46500</v>
+        <v>45500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1371,7 +1372,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1386,7 +1387,7 @@
         <v>70000</v>
       </c>
       <c r="H11">
-        <v>84000</v>
+        <v>103000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1395,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>19250</v>
+        <v>20250</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1412,7 +1413,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1427,7 +1428,7 @@
         <v>70000</v>
       </c>
       <c r="H12">
-        <v>46500</v>
+        <v>45500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1453,7 +1454,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1468,16 +1469,16 @@
         <v>70000</v>
       </c>
       <c r="H13">
-        <v>84000</v>
+        <v>120500</v>
       </c>
       <c r="I13">
-        <v>3950</v>
+        <v>200</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>5825</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1494,7 +1495,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1509,10 +1510,10 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="I14">
-        <v>637</v>
+        <v>937</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1535,7 +1536,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1550,7 +1551,7 @@
         <v>70000</v>
       </c>
       <c r="H15">
-        <v>84000</v>
+        <v>83000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1559,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1576,7 +1577,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1591,7 +1592,7 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1617,7 +1618,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1632,7 +1633,7 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>43000</v>
+        <v>42000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1658,7 +1659,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1673,7 +1674,7 @@
         <v>70000</v>
       </c>
       <c r="H18">
-        <v>43000</v>
+        <v>42000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1682,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3600</v>
+        <v>5850</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1699,7 +1700,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1740,7 +1741,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1755,7 +1756,7 @@
         <v>70000</v>
       </c>
       <c r="H20">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1781,7 +1782,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1790,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G21">
         <v>70000</v>
       </c>
       <c r="H21">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1822,7 +1823,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1837,7 +1838,7 @@
         <v>70000</v>
       </c>
       <c r="H22">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1863,7 +1864,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1878,7 +1879,7 @@
         <v>70000</v>
       </c>
       <c r="H23">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1904,7 +1905,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1919,7 +1920,7 @@
         <v>70000</v>
       </c>
       <c r="H24">
-        <v>42000</v>
+        <v>41000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1945,7 +1946,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>37500</v>
@@ -1960,7 +1961,7 @@
         <v>70000</v>
       </c>
       <c r="H25">
-        <v>99000</v>
+        <v>98000</v>
       </c>
       <c r="I25">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -971,28 +971,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1003,7 +1003,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1044,7 +1044,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1085,7 +1085,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1126,7 +1126,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1167,7 +1167,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1208,7 +1208,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1249,7 +1249,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1290,7 +1290,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1331,7 +1331,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1372,7 +1372,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1413,7 +1413,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1454,7 +1454,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1495,7 +1495,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1536,7 +1536,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1577,7 +1577,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1618,7 +1618,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1659,7 +1659,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1700,7 +1700,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1741,7 +1741,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1782,7 +1782,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1823,7 +1823,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1864,7 +1864,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1905,7 +1905,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1946,7 +1946,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -942,16 +942,9 @@
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1592,7 +1585,7 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>52000</v>
+        <v>61000</v>
       </c>
       <c r="I16">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -942,7 +942,6 @@
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
   </cols>
@@ -964,28 +963,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -996,7 +995,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1037,7 +1036,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1046,7 +1045,7 @@
         <v>41500</v>
       </c>
       <c r="F3">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G3">
         <v>70000</v>
@@ -1078,7 +1077,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1087,7 +1086,7 @@
         <v>41500</v>
       </c>
       <c r="F4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G4">
         <v>70000</v>
@@ -1119,7 +1118,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1160,7 +1159,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1201,7 +1200,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1242,7 +1241,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1251,7 +1250,7 @@
         <v>41500</v>
       </c>
       <c r="F8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G8">
         <v>70000</v>
@@ -1283,7 +1282,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1292,7 +1291,7 @@
         <v>41500</v>
       </c>
       <c r="F9">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G9">
         <v>70000</v>
@@ -1324,7 +1323,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1365,7 +1364,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1406,7 +1405,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1415,7 +1414,7 @@
         <v>41500</v>
       </c>
       <c r="F12">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G12">
         <v>70000</v>
@@ -1447,7 +1446,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1456,13 +1455,13 @@
         <v>41500</v>
       </c>
       <c r="F13">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G13">
         <v>70000</v>
       </c>
       <c r="H13">
-        <v>120500</v>
+        <v>119500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1488,7 +1487,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1497,7 +1496,7 @@
         <v>41500</v>
       </c>
       <c r="F14">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G14">
         <v>70000</v>
@@ -1529,7 +1528,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1538,7 +1537,7 @@
         <v>41500</v>
       </c>
       <c r="F15">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G15">
         <v>70000</v>
@@ -1570,7 +1569,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1579,7 +1578,7 @@
         <v>36000</v>
       </c>
       <c r="F16">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G16">
         <v>70000</v>
@@ -1611,7 +1610,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1652,7 +1651,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1661,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G18">
         <v>70000</v>
@@ -1693,7 +1692,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1734,7 +1733,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1743,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G20">
         <v>70000</v>
       </c>
       <c r="H20">
-        <v>15000</v>
+        <v>41000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1775,7 +1774,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1816,7 +1815,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1857,7 +1856,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1898,7 +1897,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1907,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G24">
         <v>70000</v>
@@ -1939,7 +1938,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -963,28 +963,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -995,7 +995,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1036,7 +1036,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1077,7 +1077,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1118,7 +1118,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1159,7 +1159,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1200,7 +1200,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1241,7 +1241,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1282,7 +1282,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1323,7 +1323,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1364,7 +1364,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1405,7 +1405,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1446,7 +1446,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1487,7 +1487,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1528,7 +1528,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1569,7 +1569,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1610,7 +1610,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1651,7 +1651,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1692,7 +1692,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1733,7 +1733,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1774,7 +1774,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1815,7 +1815,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1856,7 +1856,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1897,7 +1897,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1938,7 +1938,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -613,9 +613,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1009,8 +1012,8 @@
       <c r="G2">
         <v>70000</v>
       </c>
-      <c r="H2">
-        <v>71000</v>
+      <c r="H2" s="2">
+        <v>72000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1050,8 +1053,8 @@
       <c r="G3">
         <v>70000</v>
       </c>
-      <c r="H3">
-        <v>131525</v>
+      <c r="H3" s="2">
+        <v>133525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1091,8 +1094,8 @@
       <c r="G4">
         <v>70000</v>
       </c>
-      <c r="H4">
-        <v>96500</v>
+      <c r="H4" s="2">
+        <v>98500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1132,7 +1135,7 @@
       <c r="G5">
         <v>70000</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>43500</v>
       </c>
       <c r="I5">
@@ -1173,8 +1176,8 @@
       <c r="G6">
         <v>70000</v>
       </c>
-      <c r="H6">
-        <v>47500</v>
+      <c r="H6" s="2">
+        <v>49500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1214,8 +1217,8 @@
       <c r="G7">
         <v>70000</v>
       </c>
-      <c r="H7">
-        <v>83500</v>
+      <c r="H7" s="2">
+        <v>84500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1255,8 +1258,8 @@
       <c r="G8">
         <v>70000</v>
       </c>
-      <c r="H8">
-        <v>45500</v>
+      <c r="H8" s="2">
+        <v>47500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1296,8 +1299,8 @@
       <c r="G9">
         <v>70000</v>
       </c>
-      <c r="H9">
-        <v>110000</v>
+      <c r="H9" s="2">
+        <v>112000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1337,8 +1340,8 @@
       <c r="G10">
         <v>70000</v>
       </c>
-      <c r="H10">
-        <v>45500</v>
+      <c r="H10" s="2">
+        <v>46500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1378,7 +1381,7 @@
       <c r="G11">
         <v>70000</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>103000</v>
       </c>
       <c r="I11">
@@ -1419,8 +1422,8 @@
       <c r="G12">
         <v>70000</v>
       </c>
-      <c r="H12">
-        <v>45500</v>
+      <c r="H12" s="2">
+        <v>47500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1460,8 +1463,8 @@
       <c r="G13">
         <v>70000</v>
       </c>
-      <c r="H13">
-        <v>119500</v>
+      <c r="H13" s="2">
+        <v>121500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1501,8 +1504,8 @@
       <c r="G14">
         <v>70000</v>
       </c>
-      <c r="H14">
-        <v>82000</v>
+      <c r="H14" s="2">
+        <v>84000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1542,8 +1545,8 @@
       <c r="G15">
         <v>70000</v>
       </c>
-      <c r="H15">
-        <v>83000</v>
+      <c r="H15" s="2">
+        <v>85000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1583,8 +1586,8 @@
       <c r="G16">
         <v>70000</v>
       </c>
-      <c r="H16">
-        <v>61000</v>
+      <c r="H16" s="2">
+        <v>63000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1624,8 +1627,8 @@
       <c r="G17">
         <v>70000</v>
       </c>
-      <c r="H17">
-        <v>42000</v>
+      <c r="H17" s="2">
+        <v>43000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1665,8 +1668,8 @@
       <c r="G18">
         <v>70000</v>
       </c>
-      <c r="H18">
-        <v>42000</v>
+      <c r="H18" s="2">
+        <v>44000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1706,7 +1709,7 @@
       <c r="G19">
         <v>70000</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>0</v>
       </c>
       <c r="I19">
@@ -1747,8 +1750,8 @@
       <c r="G20">
         <v>70000</v>
       </c>
-      <c r="H20">
-        <v>41000</v>
+      <c r="H20" s="2">
+        <v>43000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1788,8 +1791,8 @@
       <c r="G21">
         <v>70000</v>
       </c>
-      <c r="H21">
-        <v>1000</v>
+      <c r="H21" s="2">
+        <v>2000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1829,8 +1832,8 @@
       <c r="G22">
         <v>70000</v>
       </c>
-      <c r="H22">
-        <v>1000</v>
+      <c r="H22" s="2">
+        <v>2000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1870,8 +1873,8 @@
       <c r="G23">
         <v>70000</v>
       </c>
-      <c r="H23">
-        <v>1000</v>
+      <c r="H23" s="2">
+        <v>2000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1911,8 +1914,8 @@
       <c r="G24">
         <v>70000</v>
       </c>
-      <c r="H24">
-        <v>41000</v>
+      <c r="H24" s="2">
+        <v>43000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1952,8 +1955,8 @@
       <c r="G25">
         <v>70000</v>
       </c>
-      <c r="H25">
-        <v>98000</v>
+      <c r="H25" s="2">
+        <v>99000</v>
       </c>
       <c r="I25">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -945,8 +945,10 @@
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1423,7 +1425,7 @@
         <v>70000</v>
       </c>
       <c r="H12" s="2">
-        <v>47500</v>
+        <v>46500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1792,7 +1794,7 @@
         <v>70000</v>
       </c>
       <c r="H21" s="2">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="I21">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -613,12 +613,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -944,11 +941,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -968,28 +960,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1000,7 +992,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1014,8 +1006,8 @@
       <c r="G2">
         <v>70000</v>
       </c>
-      <c r="H2" s="2">
-        <v>72000</v>
+      <c r="H2">
+        <v>71000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1041,7 +1033,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1055,8 +1047,8 @@
       <c r="G3">
         <v>70000</v>
       </c>
-      <c r="H3" s="2">
-        <v>133525</v>
+      <c r="H3">
+        <v>131525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1082,7 +1074,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1096,8 +1088,8 @@
       <c r="G4">
         <v>70000</v>
       </c>
-      <c r="H4" s="2">
-        <v>98500</v>
+      <c r="H4">
+        <v>96500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1123,7 +1115,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1137,7 +1129,7 @@
       <c r="G5">
         <v>70000</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>43500</v>
       </c>
       <c r="I5">
@@ -1164,7 +1156,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1178,8 +1170,8 @@
       <c r="G6">
         <v>70000</v>
       </c>
-      <c r="H6" s="2">
-        <v>49500</v>
+      <c r="H6">
+        <v>47500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1205,7 +1197,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1219,8 +1211,8 @@
       <c r="G7">
         <v>70000</v>
       </c>
-      <c r="H7" s="2">
-        <v>84500</v>
+      <c r="H7">
+        <v>83500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1246,7 +1238,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1260,8 +1252,8 @@
       <c r="G8">
         <v>70000</v>
       </c>
-      <c r="H8" s="2">
-        <v>47500</v>
+      <c r="H8">
+        <v>45500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1287,7 +1279,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1301,8 +1293,8 @@
       <c r="G9">
         <v>70000</v>
       </c>
-      <c r="H9" s="2">
-        <v>112000</v>
+      <c r="H9">
+        <v>110000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1328,7 +1320,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1342,8 +1334,8 @@
       <c r="G10">
         <v>70000</v>
       </c>
-      <c r="H10" s="2">
-        <v>46500</v>
+      <c r="H10">
+        <v>45500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1369,7 +1361,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1378,13 +1370,13 @@
         <v>41500</v>
       </c>
       <c r="F11">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G11">
         <v>70000</v>
       </c>
-      <c r="H11" s="2">
-        <v>103000</v>
+      <c r="H11">
+        <v>102000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1410,7 +1402,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1424,8 +1416,8 @@
       <c r="G12">
         <v>70000</v>
       </c>
-      <c r="H12" s="2">
-        <v>46500</v>
+      <c r="H12">
+        <v>45500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1451,7 +1443,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1465,8 +1457,8 @@
       <c r="G13">
         <v>70000</v>
       </c>
-      <c r="H13" s="2">
-        <v>121500</v>
+      <c r="H13">
+        <v>119500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1492,7 +1484,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1506,8 +1498,8 @@
       <c r="G14">
         <v>70000</v>
       </c>
-      <c r="H14" s="2">
-        <v>84000</v>
+      <c r="H14">
+        <v>82000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1533,7 +1525,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1547,8 +1539,8 @@
       <c r="G15">
         <v>70000</v>
       </c>
-      <c r="H15" s="2">
-        <v>85000</v>
+      <c r="H15">
+        <v>83000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1574,7 +1566,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1588,8 +1580,8 @@
       <c r="G16">
         <v>70000</v>
       </c>
-      <c r="H16" s="2">
-        <v>63000</v>
+      <c r="H16">
+        <v>61000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1615,7 +1607,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1629,8 +1621,8 @@
       <c r="G17">
         <v>70000</v>
       </c>
-      <c r="H17" s="2">
-        <v>43000</v>
+      <c r="H17">
+        <v>42000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1656,7 +1648,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1670,8 +1662,8 @@
       <c r="G18">
         <v>70000</v>
       </c>
-      <c r="H18" s="2">
-        <v>44000</v>
+      <c r="H18">
+        <v>42000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1697,7 +1689,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1711,7 +1703,7 @@
       <c r="G19">
         <v>70000</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
@@ -1738,7 +1730,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1752,8 +1744,8 @@
       <c r="G20">
         <v>70000</v>
       </c>
-      <c r="H20" s="2">
-        <v>43000</v>
+      <c r="H20">
+        <v>41000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1779,7 +1771,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1793,8 +1785,8 @@
       <c r="G21">
         <v>70000</v>
       </c>
-      <c r="H21" s="2">
-        <v>12000</v>
+      <c r="H21">
+        <v>10000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1820,7 +1812,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1834,8 +1826,8 @@
       <c r="G22">
         <v>70000</v>
       </c>
-      <c r="H22" s="2">
-        <v>2000</v>
+      <c r="H22">
+        <v>1000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1861,7 +1853,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1875,8 +1867,8 @@
       <c r="G23">
         <v>70000</v>
       </c>
-      <c r="H23" s="2">
-        <v>2000</v>
+      <c r="H23">
+        <v>1000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1902,7 +1894,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1916,8 +1908,8 @@
       <c r="G24">
         <v>70000</v>
       </c>
-      <c r="H24" s="2">
-        <v>43000</v>
+      <c r="H24">
+        <v>41000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1943,7 +1935,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>37500</v>
@@ -1957,8 +1949,8 @@
       <c r="G25">
         <v>70000</v>
       </c>
-      <c r="H25" s="2">
-        <v>99000</v>
+      <c r="H25">
+        <v>98000</v>
       </c>
       <c r="I25">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -613,9 +613,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1007,7 +1010,7 @@
       <c r="G2">
         <v>70000</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>71000</v>
       </c>
       <c r="I2">
@@ -1048,8 +1051,8 @@
       <c r="G3">
         <v>70000</v>
       </c>
-      <c r="H3">
-        <v>131525</v>
+      <c r="H3" s="2">
+        <v>132525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1089,8 +1092,8 @@
       <c r="G4">
         <v>70000</v>
       </c>
-      <c r="H4">
-        <v>96500</v>
+      <c r="H4" s="2">
+        <v>97500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1130,7 +1133,7 @@
       <c r="G5">
         <v>70000</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>43500</v>
       </c>
       <c r="I5">
@@ -1171,8 +1174,8 @@
       <c r="G6">
         <v>70000</v>
       </c>
-      <c r="H6">
-        <v>47500</v>
+      <c r="H6" s="2">
+        <v>48500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1212,7 +1215,7 @@
       <c r="G7">
         <v>70000</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>83500</v>
       </c>
       <c r="I7">
@@ -1253,8 +1256,8 @@
       <c r="G8">
         <v>70000</v>
       </c>
-      <c r="H8">
-        <v>45500</v>
+      <c r="H8" s="2">
+        <v>46500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1294,8 +1297,8 @@
       <c r="G9">
         <v>70000</v>
       </c>
-      <c r="H9">
-        <v>110000</v>
+      <c r="H9" s="2">
+        <v>111000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1335,7 +1338,7 @@
       <c r="G10">
         <v>70000</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>45500</v>
       </c>
       <c r="I10">
@@ -1376,8 +1379,8 @@
       <c r="G11">
         <v>70000</v>
       </c>
-      <c r="H11">
-        <v>102000</v>
+      <c r="H11" s="2">
+        <v>103000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1417,8 +1420,8 @@
       <c r="G12">
         <v>70000</v>
       </c>
-      <c r="H12">
-        <v>45500</v>
+      <c r="H12" s="2">
+        <v>46500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1458,8 +1461,8 @@
       <c r="G13">
         <v>70000</v>
       </c>
-      <c r="H13">
-        <v>119500</v>
+      <c r="H13" s="2">
+        <v>120500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1499,8 +1502,8 @@
       <c r="G14">
         <v>70000</v>
       </c>
-      <c r="H14">
-        <v>82000</v>
+      <c r="H14" s="2">
+        <v>83000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1540,8 +1543,8 @@
       <c r="G15">
         <v>70000</v>
       </c>
-      <c r="H15">
-        <v>83000</v>
+      <c r="H15" s="2">
+        <v>84000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1581,8 +1584,8 @@
       <c r="G16">
         <v>70000</v>
       </c>
-      <c r="H16">
-        <v>61000</v>
+      <c r="H16" s="2">
+        <v>62000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1622,7 +1625,7 @@
       <c r="G17">
         <v>70000</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>42000</v>
       </c>
       <c r="I17">
@@ -1663,8 +1666,8 @@
       <c r="G18">
         <v>70000</v>
       </c>
-      <c r="H18">
-        <v>42000</v>
+      <c r="H18" s="2">
+        <v>43000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1704,7 +1707,7 @@
       <c r="G19">
         <v>70000</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>0</v>
       </c>
       <c r="I19">
@@ -1745,8 +1748,8 @@
       <c r="G20">
         <v>70000</v>
       </c>
-      <c r="H20">
-        <v>41000</v>
+      <c r="H20" s="2">
+        <v>42000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1786,8 +1789,8 @@
       <c r="G21">
         <v>70000</v>
       </c>
-      <c r="H21">
-        <v>10000</v>
+      <c r="H21" s="2">
+        <v>11000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1827,7 +1830,7 @@
       <c r="G22">
         <v>70000</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>1000</v>
       </c>
       <c r="I22">
@@ -1868,7 +1871,7 @@
       <c r="G23">
         <v>70000</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>1000</v>
       </c>
       <c r="I23">
@@ -1909,8 +1912,8 @@
       <c r="G24">
         <v>70000</v>
       </c>
-      <c r="H24">
-        <v>41000</v>
+      <c r="H24" s="2">
+        <v>42000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1950,7 +1953,7 @@
       <c r="G25">
         <v>70000</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>98000</v>
       </c>
       <c r="I25">

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>business_date</t>
   </si>
@@ -106,9 +106,6 @@
   </si>
   <si>
     <t>Naggasaa Dheeressaa</t>
-  </si>
-  <si>
-    <t>Baacaa Ifaa</t>
   </si>
   <si>
     <t>Nabiyat Habtewold</t>
@@ -613,12 +610,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -940,10 +934,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -964,7 +960,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -1005,12 +1001,12 @@
         <v>41500</v>
       </c>
       <c r="F2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G2">
         <v>70000</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>71000</v>
       </c>
       <c r="I2">
@@ -1051,8 +1047,8 @@
       <c r="G3">
         <v>70000</v>
       </c>
-      <c r="H3" s="2">
-        <v>132525</v>
+      <c r="H3">
+        <v>131525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1092,8 +1088,8 @@
       <c r="G4">
         <v>70000</v>
       </c>
-      <c r="H4" s="2">
-        <v>97500</v>
+      <c r="H4">
+        <v>96500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1133,7 +1129,7 @@
       <c r="G5">
         <v>70000</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>43500</v>
       </c>
       <c r="I5">
@@ -1174,8 +1170,8 @@
       <c r="G6">
         <v>70000</v>
       </c>
-      <c r="H6" s="2">
-        <v>48500</v>
+      <c r="H6">
+        <v>47500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1210,12 +1206,12 @@
         <v>41500</v>
       </c>
       <c r="F7">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G7">
         <v>70000</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <v>83500</v>
       </c>
       <c r="I7">
@@ -1256,8 +1252,8 @@
       <c r="G8">
         <v>70000</v>
       </c>
-      <c r="H8" s="2">
-        <v>46500</v>
+      <c r="H8">
+        <v>45500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1297,8 +1293,8 @@
       <c r="G9">
         <v>70000</v>
       </c>
-      <c r="H9" s="2">
-        <v>111000</v>
+      <c r="H9">
+        <v>110000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1338,7 +1334,7 @@
       <c r="G10">
         <v>70000</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <v>45500</v>
       </c>
       <c r="I10">
@@ -1379,8 +1375,8 @@
       <c r="G11">
         <v>70000</v>
       </c>
-      <c r="H11" s="2">
-        <v>103000</v>
+      <c r="H11">
+        <v>102000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1420,8 +1416,8 @@
       <c r="G12">
         <v>70000</v>
       </c>
-      <c r="H12" s="2">
-        <v>46500</v>
+      <c r="H12">
+        <v>45500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1461,8 +1457,8 @@
       <c r="G13">
         <v>70000</v>
       </c>
-      <c r="H13" s="2">
-        <v>120500</v>
+      <c r="H13">
+        <v>119500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1502,8 +1498,8 @@
       <c r="G14">
         <v>70000</v>
       </c>
-      <c r="H14" s="2">
-        <v>83000</v>
+      <c r="H14">
+        <v>82000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1543,8 +1539,8 @@
       <c r="G15">
         <v>70000</v>
       </c>
-      <c r="H15" s="2">
-        <v>84000</v>
+      <c r="H15">
+        <v>83000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1584,8 +1580,8 @@
       <c r="G16">
         <v>70000</v>
       </c>
-      <c r="H16" s="2">
-        <v>62000</v>
+      <c r="H16">
+        <v>61000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1620,12 +1616,12 @@
         <v>14000</v>
       </c>
       <c r="F17">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G17">
         <v>70000</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>42000</v>
       </c>
       <c r="I17">
@@ -1666,8 +1662,8 @@
       <c r="G18">
         <v>70000</v>
       </c>
-      <c r="H18" s="2">
-        <v>43000</v>
+      <c r="H18">
+        <v>42000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1687,10 +1683,10 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B19">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
@@ -1702,13 +1698,13 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G19">
         <v>70000</v>
       </c>
-      <c r="H19" s="2">
-        <v>0</v>
+      <c r="H19">
+        <v>41000</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1728,10 +1724,10 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>46031</v>
+        <v>46039</v>
       </c>
       <c r="B20">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -1743,13 +1739,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G20">
         <v>70000</v>
       </c>
-      <c r="H20" s="2">
-        <v>42000</v>
+      <c r="H20">
+        <v>10000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1772,7 +1768,7 @@
         <v>46039</v>
       </c>
       <c r="B21">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
@@ -1784,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <v>2000</v>
+      </c>
+      <c r="G21">
+        <v>70000</v>
+      </c>
+      <c r="H21">
         <v>1000</v>
-      </c>
-      <c r="G21">
-        <v>70000</v>
-      </c>
-      <c r="H21" s="2">
-        <v>11000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1813,7 +1809,7 @@
         <v>46039</v>
       </c>
       <c r="B22">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
@@ -1825,12 +1821,12 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G22">
         <v>70000</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>1000</v>
       </c>
       <c r="I22">
@@ -1851,10 +1847,10 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>46039</v>
+        <v>46052</v>
       </c>
       <c r="B23">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -1866,13 +1862,13 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G23">
         <v>70000</v>
       </c>
-      <c r="H23" s="2">
-        <v>1000</v>
+      <c r="H23">
+        <v>41000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1881,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1892,10 +1888,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="B24">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
@@ -1912,8 +1908,8 @@
       <c r="G24">
         <v>70000</v>
       </c>
-      <c r="H24" s="2">
-        <v>42000</v>
+      <c r="H24">
+        <v>98000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1922,53 +1918,12 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>46057</v>
-      </c>
-      <c r="B25">
-        <v>1024</v>
-      </c>
-      <c r="C25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25">
-        <v>37500</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>2000</v>
-      </c>
-      <c r="G25">
-        <v>70000</v>
-      </c>
-      <c r="H25" s="2">
-        <v>98000</v>
-      </c>
-      <c r="I25">
-        <v>2000</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -610,9 +610,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -940,7 +943,9 @@
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1006,8 +1011,8 @@
       <c r="G2">
         <v>70000</v>
       </c>
-      <c r="H2">
-        <v>71000</v>
+      <c r="H2" s="2">
+        <v>72000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1047,8 +1052,8 @@
       <c r="G3">
         <v>70000</v>
       </c>
-      <c r="H3">
-        <v>131525</v>
+      <c r="H3" s="2">
+        <v>132525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1088,8 +1093,8 @@
       <c r="G4">
         <v>70000</v>
       </c>
-      <c r="H4">
-        <v>96500</v>
+      <c r="H4" s="2">
+        <v>97500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1129,8 +1134,8 @@
       <c r="G5">
         <v>70000</v>
       </c>
-      <c r="H5">
-        <v>43500</v>
+      <c r="H5" s="2">
+        <v>44500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1170,8 +1175,8 @@
       <c r="G6">
         <v>70000</v>
       </c>
-      <c r="H6">
-        <v>47500</v>
+      <c r="H6" s="2">
+        <v>48500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1211,8 +1216,8 @@
       <c r="G7">
         <v>70000</v>
       </c>
-      <c r="H7">
-        <v>83500</v>
+      <c r="H7" s="2">
+        <v>84500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1252,8 +1257,8 @@
       <c r="G8">
         <v>70000</v>
       </c>
-      <c r="H8">
-        <v>45500</v>
+      <c r="H8" s="2">
+        <v>46500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1293,8 +1298,8 @@
       <c r="G9">
         <v>70000</v>
       </c>
-      <c r="H9">
-        <v>110000</v>
+      <c r="H9" s="2">
+        <v>111000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1334,7 +1339,7 @@
       <c r="G10">
         <v>70000</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>45500</v>
       </c>
       <c r="I10">
@@ -1375,8 +1380,8 @@
       <c r="G11">
         <v>70000</v>
       </c>
-      <c r="H11">
-        <v>102000</v>
+      <c r="H11" s="2">
+        <v>103000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1416,8 +1421,8 @@
       <c r="G12">
         <v>70000</v>
       </c>
-      <c r="H12">
-        <v>45500</v>
+      <c r="H12" s="2">
+        <v>46500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1457,8 +1462,8 @@
       <c r="G13">
         <v>70000</v>
       </c>
-      <c r="H13">
-        <v>119500</v>
+      <c r="H13" s="2">
+        <v>120500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1498,8 +1503,8 @@
       <c r="G14">
         <v>70000</v>
       </c>
-      <c r="H14">
-        <v>82000</v>
+      <c r="H14" s="2">
+        <v>83000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1539,8 +1544,8 @@
       <c r="G15">
         <v>70000</v>
       </c>
-      <c r="H15">
-        <v>83000</v>
+      <c r="H15" s="2">
+        <v>84000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1580,8 +1585,8 @@
       <c r="G16">
         <v>70000</v>
       </c>
-      <c r="H16">
-        <v>61000</v>
+      <c r="H16" s="2">
+        <v>62000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1621,8 +1626,8 @@
       <c r="G17">
         <v>70000</v>
       </c>
-      <c r="H17">
-        <v>42000</v>
+      <c r="H17" s="2">
+        <v>43000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1662,8 +1667,8 @@
       <c r="G18">
         <v>70000</v>
       </c>
-      <c r="H18">
-        <v>42000</v>
+      <c r="H18" s="2">
+        <v>43000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1703,8 +1708,8 @@
       <c r="G19">
         <v>70000</v>
       </c>
-      <c r="H19">
-        <v>41000</v>
+      <c r="H19" s="2">
+        <v>42000</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1744,8 +1749,8 @@
       <c r="G20">
         <v>70000</v>
       </c>
-      <c r="H20">
-        <v>10000</v>
+      <c r="H20" s="2">
+        <v>11000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1785,7 +1790,7 @@
       <c r="G21">
         <v>70000</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>1000</v>
       </c>
       <c r="I21">
@@ -1826,8 +1831,8 @@
       <c r="G22">
         <v>70000</v>
       </c>
-      <c r="H22">
-        <v>1000</v>
+      <c r="H22" s="2">
+        <v>2000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1867,8 +1872,8 @@
       <c r="G23">
         <v>70000</v>
       </c>
-      <c r="H23">
-        <v>41000</v>
+      <c r="H23" s="2">
+        <v>42000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1908,8 +1913,8 @@
       <c r="G24">
         <v>70000</v>
       </c>
-      <c r="H24">
-        <v>98000</v>
+      <c r="H24" s="2">
+        <v>99000</v>
       </c>
       <c r="I24">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1012,7 +1012,7 @@
         <v>70000</v>
       </c>
       <c r="H2" s="2">
-        <v>72000</v>
+        <v>73000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1053,7 +1053,7 @@
         <v>70000</v>
       </c>
       <c r="H3" s="2">
-        <v>132525</v>
+        <v>133525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1094,7 +1094,7 @@
         <v>70000</v>
       </c>
       <c r="H4" s="2">
-        <v>97500</v>
+        <v>98500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1135,7 +1135,7 @@
         <v>70000</v>
       </c>
       <c r="H5" s="2">
-        <v>44500</v>
+        <v>45500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>70000</v>
       </c>
       <c r="H6" s="2">
-        <v>48500</v>
+        <v>49500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1217,7 +1217,7 @@
         <v>70000</v>
       </c>
       <c r="H7" s="2">
-        <v>84500</v>
+        <v>85500</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1258,7 +1258,7 @@
         <v>70000</v>
       </c>
       <c r="H8" s="2">
-        <v>46500</v>
+        <v>47500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>70000</v>
       </c>
       <c r="H9" s="2">
-        <v>111000</v>
+        <v>112000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1340,7 +1340,7 @@
         <v>70000</v>
       </c>
       <c r="H10" s="2">
-        <v>45500</v>
+        <v>46500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>70000</v>
       </c>
       <c r="H11" s="2">
-        <v>103000</v>
+        <v>104000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1422,7 +1422,7 @@
         <v>70000</v>
       </c>
       <c r="H12" s="2">
-        <v>46500</v>
+        <v>47500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1463,7 +1463,7 @@
         <v>70000</v>
       </c>
       <c r="H13" s="2">
-        <v>120500</v>
+        <v>121500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1504,7 +1504,7 @@
         <v>70000</v>
       </c>
       <c r="H14" s="2">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1545,7 +1545,7 @@
         <v>70000</v>
       </c>
       <c r="H15" s="2">
-        <v>84000</v>
+        <v>85000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1586,7 +1586,7 @@
         <v>70000</v>
       </c>
       <c r="H16" s="2">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1627,7 +1627,7 @@
         <v>70000</v>
       </c>
       <c r="H17" s="2">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1668,7 +1668,7 @@
         <v>70000</v>
       </c>
       <c r="H18" s="2">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1709,7 +1709,7 @@
         <v>70000</v>
       </c>
       <c r="H19" s="2">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1750,7 +1750,7 @@
         <v>70000</v>
       </c>
       <c r="H20" s="2">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1791,7 +1791,7 @@
         <v>70000</v>
       </c>
       <c r="H21" s="2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1832,7 +1832,7 @@
         <v>70000</v>
       </c>
       <c r="H22" s="2">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1873,7 +1873,7 @@
         <v>70000</v>
       </c>
       <c r="H23" s="2">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1914,7 +1914,7 @@
         <v>70000</v>
       </c>
       <c r="H24" s="2">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="I24">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -124,9 +127,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -610,12 +610,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -941,11 +938,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -965,39 +957,39 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>45885</v>
+        <v>45854</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1011,7 +1003,7 @@
       <c r="G2">
         <v>70000</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>73000</v>
       </c>
       <c r="I2">
@@ -1032,13 +1024,13 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1052,7 +1044,7 @@
       <c r="G3">
         <v>70000</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>133525</v>
       </c>
       <c r="I3">
@@ -1073,13 +1065,13 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>45845</v>
+        <v>45814</v>
       </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1093,8 +1085,8 @@
       <c r="G4">
         <v>70000</v>
       </c>
-      <c r="H4" s="2">
-        <v>98500</v>
+      <c r="H4">
+        <v>136500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1114,13 +1106,13 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1134,8 +1126,8 @@
       <c r="G5">
         <v>70000</v>
       </c>
-      <c r="H5" s="2">
-        <v>45500</v>
+      <c r="H5">
+        <v>46500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1155,13 +1147,13 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>45885</v>
+        <v>45854</v>
       </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1175,7 +1167,7 @@
       <c r="G6">
         <v>70000</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <v>49500</v>
       </c>
       <c r="I6">
@@ -1196,13 +1188,13 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1216,8 +1208,8 @@
       <c r="G7">
         <v>70000</v>
       </c>
-      <c r="H7" s="2">
-        <v>85500</v>
+      <c r="H7">
+        <v>123000</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1237,13 +1229,13 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1257,7 +1249,7 @@
       <c r="G8">
         <v>70000</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>47500</v>
       </c>
       <c r="I8">
@@ -1278,13 +1270,13 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1298,7 +1290,7 @@
       <c r="G9">
         <v>70000</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <v>112000</v>
       </c>
       <c r="I9">
@@ -1319,13 +1311,13 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>45849</v>
+        <v>45818</v>
       </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1339,8 +1331,8 @@
       <c r="G10">
         <v>70000</v>
       </c>
-      <c r="H10" s="2">
-        <v>46500</v>
+      <c r="H10">
+        <v>49500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1366,7 +1358,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1380,7 +1372,7 @@
       <c r="G11">
         <v>70000</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11">
         <v>104000</v>
       </c>
       <c r="I11">
@@ -1407,7 +1399,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1421,7 +1413,7 @@
       <c r="G12">
         <v>70000</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>47500</v>
       </c>
       <c r="I12">
@@ -1442,13 +1434,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>45880</v>
+        <v>45849</v>
       </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1462,7 +1454,7 @@
       <c r="G13">
         <v>70000</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>121500</v>
       </c>
       <c r="I13">
@@ -1483,13 +1475,13 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>45893</v>
+        <v>45862</v>
       </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1503,7 +1495,7 @@
       <c r="G14">
         <v>70000</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14">
         <v>84000</v>
       </c>
       <c r="I14">
@@ -1524,13 +1516,13 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>45877</v>
+        <v>45846</v>
       </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1544,7 +1536,7 @@
       <c r="G15">
         <v>70000</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <v>85000</v>
       </c>
       <c r="I15">
@@ -1571,7 +1563,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1585,8 +1577,8 @@
       <c r="G16">
         <v>70000</v>
       </c>
-      <c r="H16" s="2">
-        <v>63000</v>
+      <c r="H16">
+        <v>67000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1606,13 +1598,13 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>45997</v>
+        <v>46000</v>
       </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1626,7 +1618,7 @@
       <c r="G17">
         <v>70000</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>44000</v>
       </c>
       <c r="I17">
@@ -1653,7 +1645,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1667,7 +1659,7 @@
       <c r="G18">
         <v>70000</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <v>44000</v>
       </c>
       <c r="I18">
@@ -1694,7 +1686,7 @@
         <v>1019</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1708,7 +1700,7 @@
       <c r="G19">
         <v>70000</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>43000</v>
       </c>
       <c r="I19">
@@ -1735,7 +1727,7 @@
         <v>1020</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1749,8 +1741,8 @@
       <c r="G20">
         <v>70000</v>
       </c>
-      <c r="H20" s="2">
-        <v>12000</v>
+      <c r="H20">
+        <v>41000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1776,7 +1768,7 @@
         <v>1021</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1790,8 +1782,8 @@
       <c r="G21">
         <v>70000</v>
       </c>
-      <c r="H21" s="2">
-        <v>2000</v>
+      <c r="H21">
+        <v>3000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1817,7 +1809,7 @@
         <v>1022</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1831,8 +1823,8 @@
       <c r="G22">
         <v>70000</v>
       </c>
-      <c r="H22" s="2">
-        <v>3000</v>
+      <c r="H22">
+        <v>48000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1858,7 +1850,7 @@
         <v>1023</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1872,7 +1864,7 @@
       <c r="G23">
         <v>70000</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>43000</v>
       </c>
       <c r="I23">
@@ -1899,7 +1891,7 @@
         <v>1024</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1913,7 +1905,7 @@
       <c r="G24">
         <v>70000</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>100000</v>
       </c>
       <c r="I24">

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -936,9 +936,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1004,7 +1001,8 @@
         <v>70000</v>
       </c>
       <c r="H2">
-        <v>73000</v>
+        <f>73000+1000</f>
+        <v>74000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1045,7 +1043,8 @@
         <v>70000</v>
       </c>
       <c r="H3">
-        <v>133525</v>
+        <f>133525+1000</f>
+        <v>134525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1086,7 +1085,8 @@
         <v>70000</v>
       </c>
       <c r="H4">
-        <v>136500</v>
+        <f>136500+1000</f>
+        <v>137500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1127,7 +1127,8 @@
         <v>70000</v>
       </c>
       <c r="H5">
-        <v>46500</v>
+        <f>46500+1000</f>
+        <v>47500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1168,7 +1169,8 @@
         <v>70000</v>
       </c>
       <c r="H6">
-        <v>49500</v>
+        <f>49500+1000</f>
+        <v>50500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1209,7 +1211,8 @@
         <v>70000</v>
       </c>
       <c r="H7">
-        <v>123000</v>
+        <f>123000+1000</f>
+        <v>124000</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1250,7 +1253,8 @@
         <v>70000</v>
       </c>
       <c r="H8">
-        <v>47500</v>
+        <f>47500+1000</f>
+        <v>48500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1291,7 +1295,8 @@
         <v>70000</v>
       </c>
       <c r="H9">
-        <v>112000</v>
+        <f>112000+1000</f>
+        <v>113000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1332,7 +1337,8 @@
         <v>70000</v>
       </c>
       <c r="H10">
-        <v>49500</v>
+        <f>49500+1000</f>
+        <v>50500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1373,7 +1379,8 @@
         <v>70000</v>
       </c>
       <c r="H11">
-        <v>104000</v>
+        <f>104000+1000</f>
+        <v>105000</v>
       </c>
       <c r="I11">
         <v>4400</v>
@@ -1414,7 +1421,8 @@
         <v>70000</v>
       </c>
       <c r="H12">
-        <v>47500</v>
+        <f>47500+1000</f>
+        <v>48500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1455,7 +1463,8 @@
         <v>70000</v>
       </c>
       <c r="H13">
-        <v>121500</v>
+        <f>121500+1000</f>
+        <v>122500</v>
       </c>
       <c r="I13">
         <v>200</v>
@@ -1496,7 +1505,8 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <v>84000</v>
+        <f>84000+1000</f>
+        <v>85000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1537,7 +1547,8 @@
         <v>70000</v>
       </c>
       <c r="H15">
-        <v>85000</v>
+        <f>85000+1000</f>
+        <v>86000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1578,7 +1589,8 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>67000</v>
+        <f>67000+1000</f>
+        <v>68000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1619,7 +1631,8 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>44000</v>
+        <f>44000+1000</f>
+        <v>45000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1660,7 +1673,8 @@
         <v>70000</v>
       </c>
       <c r="H18">
-        <v>44000</v>
+        <f>44000+1000</f>
+        <v>45000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1701,7 +1715,8 @@
         <v>70000</v>
       </c>
       <c r="H19">
-        <v>43000</v>
+        <f>43000+1000</f>
+        <v>44000</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1742,7 +1757,8 @@
         <v>70000</v>
       </c>
       <c r="H20">
-        <v>41000</v>
+        <f>41000+1000</f>
+        <v>42000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1783,7 +1799,7 @@
         <v>70000</v>
       </c>
       <c r="H21">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1824,7 +1840,8 @@
         <v>70000</v>
       </c>
       <c r="H22">
-        <v>48000</v>
+        <f>48000+1000</f>
+        <v>49000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1865,7 +1882,8 @@
         <v>70000</v>
       </c>
       <c r="H23">
-        <v>43000</v>
+        <f>43000+1000</f>
+        <v>44000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1906,7 +1924,8 @@
         <v>70000</v>
       </c>
       <c r="H24">
-        <v>100000</v>
+        <f>100000+1000</f>
+        <v>101000</v>
       </c>
       <c r="I24">
         <v>2000</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -936,6 +936,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1467,7 +1470,8 @@
         <v>122500</v>
       </c>
       <c r="I13">
-        <v>200</v>
+        <f>200+700</f>
+        <v>900</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -938,6 +938,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -957,28 +959,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -989,7 +991,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1031,7 +1033,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1073,7 +1075,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1115,7 +1117,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1157,7 +1159,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1199,7 +1201,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1241,7 +1243,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1283,7 +1285,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1325,7 +1327,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1367,7 +1369,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1409,7 +1411,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1451,7 +1453,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1494,7 +1496,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1536,7 +1538,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1578,7 +1580,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1620,7 +1622,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1662,7 +1664,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1704,7 +1706,7 @@
         <v>1019</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1746,7 +1748,7 @@
         <v>1020</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1788,7 +1790,7 @@
         <v>1021</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1829,7 +1831,7 @@
         <v>1022</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1871,7 +1873,7 @@
         <v>1023</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1913,7 +1915,7 @@
         <v>1024</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\EGSA2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>business_date</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -108,6 +111,9 @@
     <t>Naggasaa Dheeressaa</t>
   </si>
   <si>
+    <t>Jaalataa magarsaa</t>
+  </si>
+  <si>
     <t>Nabiyat Habtewold</t>
   </si>
   <si>
@@ -124,9 +130,6 @@
   </si>
   <si>
     <t>Worku Guta</t>
-  </si>
-  <si>
-    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -934,12 +937,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -959,28 +962,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -991,7 +994,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1006,8 +1009,7 @@
         <v>70000</v>
       </c>
       <c r="H2">
-        <f>73000+1000</f>
-        <v>74000</v>
+        <v>73000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1033,7 +1035,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1048,8 +1050,7 @@
         <v>70000</v>
       </c>
       <c r="H3">
-        <f>133525+1000</f>
-        <v>134525</v>
+        <v>133525</v>
       </c>
       <c r="I3">
         <v>1400</v>
@@ -1075,7 +1076,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1090,8 +1091,7 @@
         <v>70000</v>
       </c>
       <c r="H4">
-        <f>136500+1000</f>
-        <v>137500</v>
+        <v>136500</v>
       </c>
       <c r="I4">
         <v>650</v>
@@ -1117,7 +1117,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1132,8 +1132,7 @@
         <v>70000</v>
       </c>
       <c r="H5">
-        <f>46500+1000</f>
-        <v>47500</v>
+        <v>46500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1159,7 +1158,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1174,8 +1173,7 @@
         <v>70000</v>
       </c>
       <c r="H6">
-        <f>49500+1000</f>
-        <v>50500</v>
+        <v>49500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1201,7 +1199,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1216,8 +1214,7 @@
         <v>70000</v>
       </c>
       <c r="H7">
-        <f>123000+1000</f>
-        <v>124000</v>
+        <v>123000</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1243,7 +1240,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1258,8 +1255,7 @@
         <v>70000</v>
       </c>
       <c r="H8">
-        <f>47500+1000</f>
-        <v>48500</v>
+        <v>47500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1285,7 +1281,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1300,8 +1296,7 @@
         <v>70000</v>
       </c>
       <c r="H9">
-        <f>112000+1000</f>
-        <v>113000</v>
+        <v>121000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1327,7 +1322,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1342,8 +1337,7 @@
         <v>70000</v>
       </c>
       <c r="H10">
-        <f>49500+1000</f>
-        <v>50500</v>
+        <v>49500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1369,7 +1363,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1384,17 +1378,16 @@
         <v>70000</v>
       </c>
       <c r="H11">
-        <f>104000+1000</f>
-        <v>105000</v>
+        <v>104000</v>
       </c>
       <c r="I11">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>20250</v>
+        <v>22625</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1411,7 +1404,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1426,8 +1419,7 @@
         <v>70000</v>
       </c>
       <c r="H12">
-        <f>47500+1000</f>
-        <v>48500</v>
+        <v>47500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1453,7 +1445,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1468,11 +1460,9 @@
         <v>70000</v>
       </c>
       <c r="H13">
-        <f>121500+1000</f>
-        <v>122500</v>
+        <v>121500</v>
       </c>
       <c r="I13">
-        <f>200+700</f>
         <v>900</v>
       </c>
       <c r="J13">
@@ -1496,7 +1486,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1511,8 +1501,7 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <f>84000+1000</f>
-        <v>85000</v>
+        <v>84000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1538,7 +1527,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1553,8 +1542,7 @@
         <v>70000</v>
       </c>
       <c r="H15">
-        <f>85000+1000</f>
-        <v>86000</v>
+        <v>85000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1580,7 +1568,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1595,8 +1583,7 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <f>67000+1000</f>
-        <v>68000</v>
+        <v>67000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1622,7 +1609,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1637,8 +1624,7 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <f>44000+1000</f>
-        <v>45000</v>
+        <v>44000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1664,7 +1650,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1679,8 +1665,7 @@
         <v>70000</v>
       </c>
       <c r="H18">
-        <f>44000+1000</f>
-        <v>45000</v>
+        <v>44000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1700,13 +1685,13 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46031</v>
+        <v>46164</v>
       </c>
       <c r="B19">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1715,14 +1700,13 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>70000</v>
       </c>
       <c r="H19">
-        <f>43000+1000</f>
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1742,13 +1726,13 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>46039</v>
+        <v>46031</v>
       </c>
       <c r="B20">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1757,14 +1741,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G20">
         <v>70000</v>
       </c>
       <c r="H20">
-        <f>41000+1000</f>
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1787,10 +1770,10 @@
         <v>46039</v>
       </c>
       <c r="B21">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1799,13 +1782,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G21">
         <v>70000</v>
       </c>
       <c r="H21">
-        <v>2000</v>
+        <v>41000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1828,10 +1811,10 @@
         <v>46039</v>
       </c>
       <c r="B22">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1840,14 +1823,13 @@
         <v>0</v>
       </c>
       <c r="F22">
+        <v>2000</v>
+      </c>
+      <c r="G22">
+        <v>70000</v>
+      </c>
+      <c r="H22">
         <v>3000</v>
-      </c>
-      <c r="G22">
-        <v>70000</v>
-      </c>
-      <c r="H22">
-        <f>48000+1000</f>
-        <v>49000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1867,13 +1849,13 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>46052</v>
+        <v>46039</v>
       </c>
       <c r="B23">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1888,8 +1870,7 @@
         <v>70000</v>
       </c>
       <c r="H23">
-        <f>43000+1000</f>
-        <v>44000</v>
+        <v>48000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1898,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1909,13 +1890,13 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="B24">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1930,8 +1911,7 @@
         <v>70000</v>
       </c>
       <c r="H24">
-        <f>100000+1000</f>
-        <v>101000</v>
+        <v>43000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1940,12 +1920,53 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B25">
+        <v>1024</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25">
+        <v>37500</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>3000</v>
+      </c>
+      <c r="G25">
+        <v>70000</v>
+      </c>
+      <c r="H25">
+        <v>100000</v>
+      </c>
+      <c r="I25">
+        <v>2000</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -943,6 +943,7 @@
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -962,28 +963,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -994,7 +995,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1035,7 +1036,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1076,7 +1077,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1117,7 +1118,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1158,7 +1159,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1199,7 +1200,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1240,7 +1241,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1281,7 +1282,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1322,7 +1323,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1363,7 +1364,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1404,7 +1405,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1445,7 +1446,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1486,7 +1487,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1527,7 +1528,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1568,7 +1569,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1609,7 +1610,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1650,7 +1651,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1691,7 +1692,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1732,7 +1733,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1773,7 +1774,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1814,7 +1815,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1855,7 +1856,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1896,7 +1897,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1937,7 +1938,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -12,14 +12,14 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025_info_w " sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>business_date</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Q1_achievement</t>
   </si>
   <si>
+    <t>Monthly_payment_Q3</t>
+  </si>
+  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -129,7 +132,10 @@
     <t>Worku Guta</t>
   </si>
   <si>
-    <t>Monthly_payment_Q2</t>
+    <t>Mange Lammaa</t>
+  </si>
+  <si>
+    <t>Katamaa Diroo</t>
   </si>
 </sst>
 </file>
@@ -937,13 +943,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -963,28 +970,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -995,7 +1002,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1010,7 +1017,7 @@
         <v>70000</v>
       </c>
       <c r="H2">
-        <v>73000</v>
+        <v>75000</v>
       </c>
       <c r="I2">
         <v>242</v>
@@ -1036,7 +1043,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1051,16 +1058,16 @@
         <v>70000</v>
       </c>
       <c r="H3">
-        <v>133525</v>
+        <v>150000</v>
       </c>
       <c r="I3">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>23625</v>
+        <v>24125</v>
       </c>
       <c r="L3">
         <v>1950</v>
@@ -1077,7 +1084,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1092,16 +1099,16 @@
         <v>70000</v>
       </c>
       <c r="H4">
-        <v>136500</v>
+        <v>150000</v>
       </c>
       <c r="I4">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>15250</v>
+        <v>16250</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1118,7 +1125,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1133,7 +1140,7 @@
         <v>70000</v>
       </c>
       <c r="H5">
-        <v>46500</v>
+        <v>47500</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1159,7 +1166,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1174,7 +1181,7 @@
         <v>70000</v>
       </c>
       <c r="H6">
-        <v>49500</v>
+        <v>51500</v>
       </c>
       <c r="I6">
         <v>892</v>
@@ -1200,7 +1207,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1215,7 +1222,7 @@
         <v>70000</v>
       </c>
       <c r="H7">
-        <v>123000</v>
+        <v>127000</v>
       </c>
       <c r="I7">
         <v>650</v>
@@ -1241,7 +1248,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1256,7 +1263,7 @@
         <v>70000</v>
       </c>
       <c r="H8">
-        <v>47500</v>
+        <v>49500</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1282,7 +1289,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1297,7 +1304,7 @@
         <v>70000</v>
       </c>
       <c r="H9">
-        <v>121000</v>
+        <v>123000</v>
       </c>
       <c r="I9">
         <v>650</v>
@@ -1323,7 +1330,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1338,7 +1345,7 @@
         <v>70000</v>
       </c>
       <c r="H10">
-        <v>49500</v>
+        <v>50500</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1364,7 +1371,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1379,7 +1386,7 @@
         <v>70000</v>
       </c>
       <c r="H11">
-        <v>104000</v>
+        <v>105000</v>
       </c>
       <c r="I11">
         <v>5100</v>
@@ -1405,7 +1412,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1420,7 +1427,7 @@
         <v>70000</v>
       </c>
       <c r="H12">
-        <v>47500</v>
+        <v>49500</v>
       </c>
       <c r="I12">
         <v>700</v>
@@ -1446,7 +1453,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1461,7 +1468,7 @@
         <v>70000</v>
       </c>
       <c r="H13">
-        <v>121500</v>
+        <v>123500</v>
       </c>
       <c r="I13">
         <v>900</v>
@@ -1487,7 +1494,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1502,7 +1509,7 @@
         <v>70000</v>
       </c>
       <c r="H14">
-        <v>84000</v>
+        <v>86000</v>
       </c>
       <c r="I14">
         <v>937</v>
@@ -1528,7 +1535,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1543,7 +1550,7 @@
         <v>70000</v>
       </c>
       <c r="H15">
-        <v>85000</v>
+        <v>87000</v>
       </c>
       <c r="I15">
         <v>1250</v>
@@ -1569,7 +1576,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1584,7 +1591,7 @@
         <v>70000</v>
       </c>
       <c r="H16">
-        <v>67000</v>
+        <v>73000</v>
       </c>
       <c r="I16">
         <v>2000</v>
@@ -1610,7 +1617,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1625,7 +1632,7 @@
         <v>70000</v>
       </c>
       <c r="H17">
-        <v>44000</v>
+        <v>45000</v>
       </c>
       <c r="I17">
         <v>2000</v>
@@ -1651,7 +1658,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1666,7 +1673,7 @@
         <v>70000</v>
       </c>
       <c r="H18">
-        <v>44000</v>
+        <v>46000</v>
       </c>
       <c r="I18">
         <v>2400</v>
@@ -1692,7 +1699,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1707,7 +1714,7 @@
         <v>70000</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I19">
         <v>2000</v>
@@ -1733,7 +1740,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1748,7 +1755,7 @@
         <v>70000</v>
       </c>
       <c r="H20">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="I20">
         <v>2000</v>
@@ -1774,7 +1781,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1789,7 +1796,7 @@
         <v>70000</v>
       </c>
       <c r="H21">
-        <v>41000</v>
+        <v>43000</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -1815,7 +1822,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1830,7 +1837,7 @@
         <v>70000</v>
       </c>
       <c r="H22">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -1856,7 +1863,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1871,7 +1878,7 @@
         <v>70000</v>
       </c>
       <c r="H23">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -1897,7 +1904,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1912,7 +1919,7 @@
         <v>70000</v>
       </c>
       <c r="H24">
-        <v>43000</v>
+        <v>45000</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -1938,7 +1945,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>37500</v>
@@ -1953,7 +1960,7 @@
         <v>70000</v>
       </c>
       <c r="H25">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="I25">
         <v>2000</v>
@@ -1968,6 +1975,88 @@
         <v>0</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B26">
+        <v>1025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26">
+        <v>37500</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>70000</v>
+      </c>
+      <c r="H26">
+        <v>41000</v>
+      </c>
+      <c r="I26">
+        <v>2500</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>500</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B27">
+        <v>1026</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27">
+        <v>37500</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>70000</v>
+      </c>
+      <c r="H27">
+        <v>43000</v>
+      </c>
+      <c r="I27">
+        <v>2000</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info_w.xlsx
+++ b/EGSA2025_info_w.xlsx
@@ -36,9 +36,6 @@
     <t>Q1_achievement</t>
   </si>
   <si>
-    <t>Monthly_payment_Q3</t>
-  </si>
-  <si>
     <t>Q2_plan</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>Katamaa Diroo</t>
+  </si>
+  <si>
+    <t>Monthly_payment_Q2</t>
   </si>
 </sst>
 </file>
@@ -968,28 +968,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1000,7 +1000,7 @@
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>37500</v>
@@ -1041,7 +1041,7 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>37500</v>
@@ -1082,7 +1082,7 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>37500</v>
@@ -1123,7 +1123,7 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>37500</v>
@@ -1164,7 +1164,7 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>37500</v>
@@ -1205,7 +1205,7 @@
         <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>37500</v>
@@ -1246,7 +1246,7 @@
         <v>1007</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>37500</v>
@@ -1287,7 +1287,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>37500</v>
@@ -1328,7 +1328,7 @@
         <v>1009</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>37500</v>
@@ -1369,7 +1369,7 @@
         <v>1010</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>37500</v>
@@ -1410,7 +1410,7 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>37500</v>
@@ -1451,7 +1451,7 @@
         <v>1012</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>37500</v>
@@ -1492,7 +1492,7 @@
         <v>1013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>37500</v>
@@ -1533,7 +1533,7 @@
         <v>1014</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>37500</v>
@@ -1574,7 +1574,7 @@
         <v>1015</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>37500</v>
@@ -1615,7 +1615,7 @@
         <v>1016</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>37500</v>
@@ -1656,7 +1656,7 @@
         <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>37500</v>
@@ -1697,7 +1697,7 @@
         <v>1018</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>37500</v>
@@ -1738,7 +1738,7 @@
         <v>1019</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>37500</v>
@@ -1779,7 +1779,7 @@
         <v>1020</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>37500</v>
@@ -1820,7 +1820,7 @@
         <v>1021</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>37500</v>
@@ -1861,7 +1861,7 @@
         <v>1022</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>37500</v>
@@ -1902,7 +1902,7 @@
         <v>1023</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>37500</v>
@@ -1943,7 +1943,7 @@
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>37500</v>
@@ -1984,7 +1984,7 @@
         <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26">
         <v>37500</v>
@@ -2025,7 +2025,7 @@
         <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27">
         <v>37500</v>
